--- a/tools/metropolis-map.xlsx
+++ b/tools/metropolis-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaika\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{232BCFED-9029-43E8-8B85-82A4AFE31DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C121D679-BB4A-4670-B2BC-B91FD9167C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{FDB3F59F-2382-4AC6-AB9E-518BB5CABC43}"/>
+    <workbookView xWindow="5070" yWindow="0" windowWidth="21600" windowHeight="11835" xr2:uid="{FDB3F59F-2382-4AC6-AB9E-518BB5CABC43}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -107,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -130,13 +130,252 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -162,6 +401,63 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2033,82 +2329,82 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
-      <c r="AF17" s="4"/>
-      <c r="AG17" s="4"/>
-      <c r="AH17" s="4"/>
-      <c r="AI17" s="4"/>
-      <c r="AJ17" s="4"/>
-      <c r="AK17" s="4"/>
-      <c r="AL17" s="4"/>
-      <c r="AM17" s="4"/>
-      <c r="AN17" s="4"/>
-      <c r="AO17" s="4"/>
-      <c r="AP17" s="4"/>
-      <c r="AQ17" s="4"/>
-      <c r="AR17" s="4"/>
-      <c r="AS17" s="4"/>
-      <c r="AT17" s="4"/>
-      <c r="AU17" s="4"/>
-      <c r="AV17" s="4"/>
-      <c r="AW17" s="4"/>
-      <c r="AX17" s="4"/>
-      <c r="AY17" s="4"/>
-      <c r="AZ17" s="4"/>
-      <c r="BA17" s="4"/>
-      <c r="BB17" s="4"/>
-      <c r="BC17" s="4"/>
-      <c r="BD17" s="4"/>
-      <c r="BE17" s="4"/>
-      <c r="BF17" s="4"/>
-      <c r="BG17" s="4"/>
-      <c r="BH17" s="4"/>
-      <c r="BI17" s="4"/>
-      <c r="BJ17" s="4"/>
-      <c r="BK17" s="4"/>
-      <c r="BL17" s="4"/>
-      <c r="BM17" s="4"/>
-      <c r="BN17" s="4"/>
-      <c r="BO17" s="4"/>
-      <c r="BP17" s="4"/>
-      <c r="BQ17" s="4"/>
-      <c r="BR17" s="4"/>
-      <c r="BS17" s="4"/>
-      <c r="BT17" s="4"/>
-      <c r="BU17" s="4"/>
-      <c r="BV17" s="4"/>
-      <c r="BW17" s="4"/>
-      <c r="BX17" s="4"/>
-      <c r="BY17" s="4"/>
-      <c r="BZ17" s="4"/>
-      <c r="CA17" s="4"/>
-      <c r="CB17" s="4"/>
-      <c r="CC17" s="4"/>
-      <c r="CD17" s="4"/>
-      <c r="CE17" s="4"/>
-      <c r="CF17" s="4"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="2"/>
+      <c r="AE17" s="2"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="2"/>
+      <c r="AH17" s="2"/>
+      <c r="AI17" s="2"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="2"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+      <c r="AP17" s="2"/>
+      <c r="AQ17" s="2"/>
+      <c r="AR17" s="2"/>
+      <c r="AS17" s="2"/>
+      <c r="AT17" s="2"/>
+      <c r="AU17" s="2"/>
+      <c r="AV17" s="2"/>
+      <c r="AW17" s="2"/>
+      <c r="AX17" s="2"/>
+      <c r="AY17" s="2"/>
+      <c r="AZ17" s="2"/>
+      <c r="BA17" s="2"/>
+      <c r="BB17" s="2"/>
+      <c r="BC17" s="2"/>
+      <c r="BD17" s="2"/>
+      <c r="BE17" s="2"/>
+      <c r="BF17" s="2"/>
+      <c r="BG17" s="2"/>
+      <c r="BH17" s="2"/>
+      <c r="BI17" s="2"/>
+      <c r="BJ17" s="2"/>
+      <c r="BK17" s="2"/>
+      <c r="BL17" s="2"/>
+      <c r="BM17" s="2"/>
+      <c r="BN17" s="2"/>
+      <c r="BO17" s="2"/>
+      <c r="BP17" s="2"/>
+      <c r="BQ17" s="2"/>
+      <c r="BR17" s="2"/>
+      <c r="BS17" s="2"/>
+      <c r="BT17" s="2"/>
+      <c r="BU17" s="2"/>
+      <c r="BV17" s="2"/>
+      <c r="BW17" s="2"/>
+      <c r="BX17" s="2"/>
+      <c r="BY17" s="2"/>
+      <c r="BZ17" s="2"/>
+      <c r="CA17" s="2"/>
+      <c r="CB17" s="2"/>
+      <c r="CC17" s="2"/>
+      <c r="CD17" s="2"/>
+      <c r="CE17" s="2"/>
+      <c r="CF17" s="2"/>
       <c r="CG17" s="2"/>
       <c r="CH17" s="2"/>
       <c r="CI17" s="2"/>
@@ -2124,89 +2420,89 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
-      <c r="AF18" s="4"/>
-      <c r="AG18" s="4"/>
-      <c r="AH18" s="4"/>
-      <c r="AI18" s="4"/>
-      <c r="AJ18" s="4"/>
-      <c r="AK18" s="4"/>
-      <c r="AL18" s="4"/>
-      <c r="AM18" s="4"/>
-      <c r="AN18" s="4"/>
-      <c r="AO18" s="4"/>
-      <c r="AP18" s="4"/>
-      <c r="AQ18" s="4"/>
-      <c r="AR18" s="4"/>
-      <c r="AS18" s="4"/>
-      <c r="AT18" s="4"/>
-      <c r="AU18" s="4"/>
-      <c r="AV18" s="4"/>
-      <c r="AW18" s="4"/>
-      <c r="AX18" s="4"/>
-      <c r="AY18" s="4"/>
-      <c r="AZ18" s="4"/>
-      <c r="BA18" s="4"/>
-      <c r="BB18" s="4"/>
-      <c r="BC18" s="4"/>
-      <c r="BD18" s="4"/>
-      <c r="BE18" s="4"/>
-      <c r="BF18" s="4"/>
-      <c r="BG18" s="4"/>
-      <c r="BH18" s="4"/>
-      <c r="BI18" s="4"/>
-      <c r="BJ18" s="4"/>
-      <c r="BK18" s="4"/>
-      <c r="BL18" s="4"/>
-      <c r="BM18" s="4"/>
-      <c r="BN18" s="4"/>
-      <c r="BO18" s="4"/>
-      <c r="BP18" s="4"/>
-      <c r="BQ18" s="4"/>
-      <c r="BR18" s="4"/>
-      <c r="BS18" s="4"/>
-      <c r="BT18" s="4"/>
-      <c r="BU18" s="4"/>
-      <c r="BV18" s="4"/>
-      <c r="BW18" s="4"/>
-      <c r="BX18" s="4"/>
-      <c r="BY18" s="4"/>
-      <c r="BZ18" s="4"/>
-      <c r="CA18" s="4"/>
-      <c r="CB18" s="4"/>
-      <c r="CC18" s="4"/>
-      <c r="CD18" s="4"/>
-      <c r="CE18" s="4"/>
-      <c r="CF18" s="4"/>
-      <c r="CG18" s="4"/>
-      <c r="CH18" s="4"/>
-      <c r="CI18" s="4"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="2"/>
+      <c r="AR18" s="2"/>
+      <c r="AS18" s="2"/>
+      <c r="AT18" s="2"/>
+      <c r="AU18" s="2"/>
+      <c r="AV18" s="2"/>
+      <c r="AW18" s="2"/>
+      <c r="AX18" s="2"/>
+      <c r="AY18" s="2"/>
+      <c r="AZ18" s="2"/>
+      <c r="BA18" s="2"/>
+      <c r="BB18" s="2"/>
+      <c r="BC18" s="2"/>
+      <c r="BD18" s="2"/>
+      <c r="BE18" s="2"/>
+      <c r="BF18" s="2"/>
+      <c r="BG18" s="2"/>
+      <c r="BH18" s="2"/>
+      <c r="BI18" s="2"/>
+      <c r="BJ18" s="2"/>
+      <c r="BK18" s="2"/>
+      <c r="BL18" s="2"/>
+      <c r="BM18" s="2"/>
+      <c r="BN18" s="2"/>
+      <c r="BO18" s="2"/>
+      <c r="BP18" s="2"/>
+      <c r="BQ18" s="2"/>
+      <c r="BR18" s="2"/>
+      <c r="BS18" s="2"/>
+      <c r="BT18" s="2"/>
+      <c r="BU18" s="2"/>
+      <c r="BV18" s="2"/>
+      <c r="BW18" s="2"/>
+      <c r="BX18" s="2"/>
+      <c r="BY18" s="2"/>
+      <c r="BZ18" s="2"/>
+      <c r="CA18" s="2"/>
+      <c r="CB18" s="2"/>
+      <c r="CC18" s="2"/>
+      <c r="CD18" s="2"/>
+      <c r="CE18" s="2"/>
+      <c r="CF18" s="2"/>
+      <c r="CG18" s="2"/>
+      <c r="CH18" s="2"/>
+      <c r="CI18" s="2"/>
       <c r="CJ18" s="2"/>
       <c r="CK18" s="2"/>
       <c r="CL18" s="2"/>
@@ -2219,90 +2515,90 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="4"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="4"/>
-      <c r="AP19" s="4"/>
-      <c r="AQ19" s="4"/>
-      <c r="AR19" s="4"/>
-      <c r="AS19" s="4"/>
-      <c r="AT19" s="4"/>
-      <c r="AU19" s="4"/>
-      <c r="AV19" s="4"/>
-      <c r="AW19" s="4"/>
-      <c r="AX19" s="4"/>
-      <c r="AY19" s="4"/>
-      <c r="AZ19" s="4"/>
-      <c r="BA19" s="4"/>
-      <c r="BB19" s="4"/>
-      <c r="BC19" s="4"/>
-      <c r="BD19" s="4"/>
-      <c r="BE19" s="4"/>
-      <c r="BF19" s="4"/>
-      <c r="BG19" s="4"/>
-      <c r="BH19" s="4"/>
-      <c r="BI19" s="4"/>
-      <c r="BJ19" s="4"/>
-      <c r="BK19" s="4"/>
-      <c r="BL19" s="4"/>
-      <c r="BM19" s="4"/>
-      <c r="BN19" s="4"/>
-      <c r="BO19" s="4"/>
-      <c r="BP19" s="4"/>
-      <c r="BQ19" s="4"/>
-      <c r="BR19" s="4"/>
-      <c r="BS19" s="4"/>
-      <c r="BT19" s="4"/>
-      <c r="BU19" s="4"/>
-      <c r="BV19" s="4"/>
-      <c r="BW19" s="4"/>
-      <c r="BX19" s="4"/>
-      <c r="BY19" s="4"/>
-      <c r="BZ19" s="4"/>
-      <c r="CA19" s="4"/>
-      <c r="CB19" s="4"/>
-      <c r="CC19" s="4"/>
-      <c r="CD19" s="4"/>
-      <c r="CE19" s="4"/>
-      <c r="CF19" s="4"/>
-      <c r="CG19" s="4"/>
-      <c r="CH19" s="4"/>
-      <c r="CI19" s="4"/>
-      <c r="CJ19" s="4"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="2"/>
+      <c r="AR19" s="2"/>
+      <c r="AS19" s="2"/>
+      <c r="AT19" s="2"/>
+      <c r="AU19" s="2"/>
+      <c r="AV19" s="2"/>
+      <c r="AW19" s="2"/>
+      <c r="AX19" s="2"/>
+      <c r="AY19" s="2"/>
+      <c r="AZ19" s="2"/>
+      <c r="BA19" s="2"/>
+      <c r="BB19" s="2"/>
+      <c r="BC19" s="2"/>
+      <c r="BD19" s="2"/>
+      <c r="BE19" s="2"/>
+      <c r="BF19" s="2"/>
+      <c r="BG19" s="2"/>
+      <c r="BH19" s="2"/>
+      <c r="BI19" s="2"/>
+      <c r="BJ19" s="2"/>
+      <c r="BK19" s="2"/>
+      <c r="BL19" s="2"/>
+      <c r="BM19" s="2"/>
+      <c r="BN19" s="2"/>
+      <c r="BO19" s="2"/>
+      <c r="BP19" s="2"/>
+      <c r="BQ19" s="2"/>
+      <c r="BR19" s="2"/>
+      <c r="BS19" s="2"/>
+      <c r="BT19" s="2"/>
+      <c r="BU19" s="2"/>
+      <c r="BV19" s="2"/>
+      <c r="BW19" s="2"/>
+      <c r="BX19" s="2"/>
+      <c r="BY19" s="2"/>
+      <c r="BZ19" s="2"/>
+      <c r="CA19" s="2"/>
+      <c r="CB19" s="2"/>
+      <c r="CC19" s="2"/>
+      <c r="CD19" s="2"/>
+      <c r="CE19" s="2"/>
+      <c r="CF19" s="2"/>
+      <c r="CG19" s="2"/>
+      <c r="CH19" s="2"/>
+      <c r="CI19" s="2"/>
+      <c r="CJ19" s="2"/>
       <c r="CK19" s="2"/>
       <c r="CL19" s="2"/>
       <c r="CM19" s="2"/>
@@ -2313,91 +2609,91 @@
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
-      <c r="AB20" s="4"/>
-      <c r="AC20" s="4"/>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="5"/>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
-      <c r="AI20" s="5"/>
-      <c r="AJ20" s="5"/>
-      <c r="AK20" s="5"/>
-      <c r="AL20" s="5"/>
-      <c r="AM20" s="5"/>
-      <c r="AN20" s="5"/>
-      <c r="AO20" s="5"/>
-      <c r="AP20" s="5"/>
-      <c r="AQ20" s="5"/>
-      <c r="AR20" s="5"/>
-      <c r="AS20" s="5"/>
-      <c r="AT20" s="5"/>
-      <c r="AU20" s="5"/>
-      <c r="AV20" s="5"/>
-      <c r="AW20" s="5"/>
-      <c r="AX20" s="5"/>
-      <c r="AY20" s="5"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
-      <c r="BE20" s="5"/>
-      <c r="BF20" s="5"/>
-      <c r="BG20" s="5"/>
-      <c r="BH20" s="5"/>
-      <c r="BI20" s="5"/>
-      <c r="BJ20" s="5"/>
-      <c r="BK20" s="5"/>
-      <c r="BL20" s="5"/>
-      <c r="BM20" s="5"/>
-      <c r="BN20" s="5"/>
-      <c r="BO20" s="5"/>
-      <c r="BP20" s="5"/>
-      <c r="BQ20" s="5"/>
-      <c r="BR20" s="5"/>
-      <c r="BS20" s="4"/>
-      <c r="BT20" s="4"/>
-      <c r="BU20" s="4"/>
-      <c r="BV20" s="4"/>
-      <c r="BW20" s="4"/>
-      <c r="BX20" s="4"/>
-      <c r="BY20" s="4"/>
-      <c r="BZ20" s="4"/>
-      <c r="CA20" s="4"/>
-      <c r="CB20" s="4"/>
-      <c r="CC20" s="4"/>
-      <c r="CD20" s="4"/>
-      <c r="CE20" s="4"/>
-      <c r="CF20" s="4"/>
-      <c r="CG20" s="4"/>
-      <c r="CH20" s="4"/>
-      <c r="CI20" s="4"/>
-      <c r="CJ20" s="4"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AI20" s="2"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="2"/>
+      <c r="AL20" s="2"/>
+      <c r="AM20" s="2"/>
+      <c r="AN20" s="2"/>
+      <c r="AO20" s="2"/>
+      <c r="AP20" s="2"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2"/>
+      <c r="AS20" s="2"/>
+      <c r="AT20" s="2"/>
+      <c r="AU20" s="2"/>
+      <c r="AV20" s="2"/>
+      <c r="AW20" s="2"/>
+      <c r="AX20" s="2"/>
+      <c r="AY20" s="2"/>
+      <c r="AZ20" s="2"/>
+      <c r="BA20" s="2"/>
+      <c r="BB20" s="2"/>
+      <c r="BC20" s="2"/>
+      <c r="BD20" s="2"/>
+      <c r="BE20" s="2"/>
+      <c r="BF20" s="2"/>
+      <c r="BG20" s="2"/>
+      <c r="BH20" s="2"/>
+      <c r="BI20" s="2"/>
+      <c r="BJ20" s="2"/>
+      <c r="BK20" s="2"/>
+      <c r="BL20" s="2"/>
+      <c r="BM20" s="2"/>
+      <c r="BN20" s="2"/>
+      <c r="BO20" s="2"/>
+      <c r="BP20" s="2"/>
+      <c r="BQ20" s="2"/>
+      <c r="BR20" s="2"/>
+      <c r="BS20" s="2"/>
+      <c r="BT20" s="2"/>
+      <c r="BU20" s="2"/>
+      <c r="BV20" s="2"/>
+      <c r="BW20" s="2"/>
+      <c r="BX20" s="2"/>
+      <c r="BY20" s="2"/>
+      <c r="BZ20" s="2"/>
+      <c r="CA20" s="2"/>
+      <c r="CB20" s="2"/>
+      <c r="CC20" s="2"/>
+      <c r="CD20" s="2"/>
+      <c r="CE20" s="2"/>
+      <c r="CF20" s="2"/>
+      <c r="CG20" s="2"/>
+      <c r="CH20" s="2"/>
+      <c r="CI20" s="2"/>
+      <c r="CJ20" s="2"/>
       <c r="CK20" s="2"/>
       <c r="CL20" s="2"/>
       <c r="CM20" s="2"/>
@@ -2408,91 +2704,91 @@
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="5"/>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="5"/>
-      <c r="AJ21" s="5"/>
-      <c r="AK21" s="5"/>
-      <c r="AL21" s="5"/>
-      <c r="AM21" s="5"/>
-      <c r="AN21" s="5"/>
-      <c r="AO21" s="5"/>
-      <c r="AP21" s="5"/>
-      <c r="AQ21" s="5"/>
-      <c r="AR21" s="5"/>
-      <c r="AS21" s="5"/>
-      <c r="AT21" s="5"/>
-      <c r="AU21" s="5"/>
-      <c r="AV21" s="5"/>
-      <c r="AW21" s="5"/>
-      <c r="AX21" s="5"/>
-      <c r="AY21" s="5"/>
-      <c r="AZ21" s="5"/>
-      <c r="BA21" s="5"/>
-      <c r="BB21" s="5"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="5"/>
-      <c r="BE21" s="5"/>
-      <c r="BF21" s="5"/>
-      <c r="BG21" s="5"/>
-      <c r="BH21" s="5"/>
-      <c r="BI21" s="5"/>
-      <c r="BJ21" s="5"/>
-      <c r="BK21" s="5"/>
-      <c r="BL21" s="5"/>
-      <c r="BM21" s="5"/>
-      <c r="BN21" s="5"/>
-      <c r="BO21" s="5"/>
-      <c r="BP21" s="5"/>
-      <c r="BQ21" s="5"/>
-      <c r="BR21" s="5"/>
-      <c r="BS21" s="5"/>
-      <c r="BT21" s="5"/>
-      <c r="BU21" s="5"/>
-      <c r="BV21" s="5"/>
-      <c r="BW21" s="5"/>
-      <c r="BX21" s="5"/>
-      <c r="BY21" s="5"/>
-      <c r="BZ21" s="5"/>
-      <c r="CA21" s="5"/>
-      <c r="CB21" s="4"/>
-      <c r="CC21" s="4"/>
-      <c r="CD21" s="4"/>
-      <c r="CE21" s="4"/>
-      <c r="CF21" s="4"/>
-      <c r="CG21" s="4"/>
-      <c r="CH21" s="4"/>
-      <c r="CI21" s="4"/>
-      <c r="CJ21" s="4"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="2"/>
+      <c r="AF21" s="2"/>
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2"/>
+      <c r="AJ21" s="2"/>
+      <c r="AK21" s="2"/>
+      <c r="AL21" s="2"/>
+      <c r="AM21" s="2"/>
+      <c r="AN21" s="2"/>
+      <c r="AO21" s="2"/>
+      <c r="AP21" s="2"/>
+      <c r="AQ21" s="2"/>
+      <c r="AR21" s="2"/>
+      <c r="AS21" s="2"/>
+      <c r="AT21" s="2"/>
+      <c r="AU21" s="2"/>
+      <c r="AV21" s="2"/>
+      <c r="AW21" s="2"/>
+      <c r="AX21" s="2"/>
+      <c r="AY21" s="2"/>
+      <c r="AZ21" s="2"/>
+      <c r="BA21" s="2"/>
+      <c r="BB21" s="2"/>
+      <c r="BC21" s="2"/>
+      <c r="BD21" s="2"/>
+      <c r="BE21" s="2"/>
+      <c r="BF21" s="2"/>
+      <c r="BG21" s="2"/>
+      <c r="BH21" s="2"/>
+      <c r="BI21" s="2"/>
+      <c r="BJ21" s="2"/>
+      <c r="BK21" s="2"/>
+      <c r="BL21" s="2"/>
+      <c r="BM21" s="2"/>
+      <c r="BN21" s="2"/>
+      <c r="BO21" s="2"/>
+      <c r="BP21" s="2"/>
+      <c r="BQ21" s="2"/>
+      <c r="BR21" s="2"/>
+      <c r="BS21" s="2"/>
+      <c r="BT21" s="2"/>
+      <c r="BU21" s="2"/>
+      <c r="BV21" s="2"/>
+      <c r="BW21" s="2"/>
+      <c r="BX21" s="2"/>
+      <c r="BY21" s="2"/>
+      <c r="BZ21" s="2"/>
+      <c r="CA21" s="2"/>
+      <c r="CB21" s="2"/>
+      <c r="CC21" s="2"/>
+      <c r="CD21" s="2"/>
+      <c r="CE21" s="2"/>
+      <c r="CF21" s="2"/>
+      <c r="CG21" s="2"/>
+      <c r="CH21" s="2"/>
+      <c r="CI21" s="2"/>
+      <c r="CJ21" s="2"/>
       <c r="CK21" s="2"/>
       <c r="CL21" s="2"/>
       <c r="CM21" s="2"/>
@@ -2503,91 +2799,91 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="5"/>
-      <c r="AH22" s="5"/>
-      <c r="AI22" s="5"/>
-      <c r="AJ22" s="5"/>
-      <c r="AK22" s="5"/>
-      <c r="AL22" s="5"/>
-      <c r="AM22" s="5"/>
-      <c r="AN22" s="5"/>
-      <c r="AO22" s="5"/>
-      <c r="AP22" s="5"/>
-      <c r="AQ22" s="5"/>
-      <c r="AR22" s="5"/>
-      <c r="AS22" s="5"/>
-      <c r="AT22" s="5"/>
-      <c r="AU22" s="5"/>
-      <c r="AV22" s="5"/>
-      <c r="AW22" s="5"/>
-      <c r="AX22" s="5"/>
-      <c r="AY22" s="5"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="5"/>
-      <c r="BB22" s="5"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="5"/>
-      <c r="BE22" s="5"/>
-      <c r="BF22" s="5"/>
-      <c r="BG22" s="5"/>
-      <c r="BH22" s="5"/>
-      <c r="BI22" s="5"/>
-      <c r="BJ22" s="5"/>
-      <c r="BK22" s="5"/>
-      <c r="BL22" s="5"/>
-      <c r="BM22" s="5"/>
-      <c r="BN22" s="5"/>
-      <c r="BO22" s="5"/>
-      <c r="BP22" s="5"/>
-      <c r="BQ22" s="5"/>
-      <c r="BR22" s="5"/>
-      <c r="BS22" s="5"/>
-      <c r="BT22" s="5"/>
-      <c r="BU22" s="5"/>
-      <c r="BV22" s="5"/>
-      <c r="BW22" s="5"/>
-      <c r="BX22" s="5"/>
-      <c r="BY22" s="5"/>
-      <c r="BZ22" s="5"/>
-      <c r="CA22" s="5"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="4"/>
-      <c r="CG22" s="4"/>
-      <c r="CH22" s="4"/>
-      <c r="CI22" s="4"/>
-      <c r="CJ22" s="4"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="2"/>
+      <c r="AF22" s="2"/>
+      <c r="AG22" s="2"/>
+      <c r="AH22" s="2"/>
+      <c r="AI22" s="2"/>
+      <c r="AJ22" s="2"/>
+      <c r="AK22" s="2"/>
+      <c r="AL22" s="2"/>
+      <c r="AM22" s="2"/>
+      <c r="AN22" s="2"/>
+      <c r="AO22" s="2"/>
+      <c r="AP22" s="2"/>
+      <c r="AQ22" s="2"/>
+      <c r="AR22" s="2"/>
+      <c r="AS22" s="2"/>
+      <c r="AT22" s="2"/>
+      <c r="AU22" s="2"/>
+      <c r="AV22" s="2"/>
+      <c r="AW22" s="2"/>
+      <c r="AX22" s="2"/>
+      <c r="AY22" s="2"/>
+      <c r="AZ22" s="2"/>
+      <c r="BA22" s="2"/>
+      <c r="BB22" s="2"/>
+      <c r="BC22" s="2"/>
+      <c r="BD22" s="2"/>
+      <c r="BE22" s="2"/>
+      <c r="BF22" s="2"/>
+      <c r="BG22" s="2"/>
+      <c r="BH22" s="2"/>
+      <c r="BI22" s="2"/>
+      <c r="BJ22" s="2"/>
+      <c r="BK22" s="2"/>
+      <c r="BL22" s="2"/>
+      <c r="BM22" s="2"/>
+      <c r="BN22" s="2"/>
+      <c r="BO22" s="2"/>
+      <c r="BP22" s="2"/>
+      <c r="BQ22" s="2"/>
+      <c r="BR22" s="2"/>
+      <c r="BS22" s="2"/>
+      <c r="BT22" s="2"/>
+      <c r="BU22" s="2"/>
+      <c r="BV22" s="2"/>
+      <c r="BW22" s="2"/>
+      <c r="BX22" s="2"/>
+      <c r="BY22" s="2"/>
+      <c r="BZ22" s="2"/>
+      <c r="CA22" s="2"/>
+      <c r="CB22" s="2"/>
+      <c r="CC22" s="2"/>
+      <c r="CD22" s="2"/>
+      <c r="CE22" s="2"/>
+      <c r="CF22" s="2"/>
+      <c r="CG22" s="2"/>
+      <c r="CH22" s="2"/>
+      <c r="CI22" s="2"/>
+      <c r="CJ22" s="2"/>
       <c r="CK22" s="2"/>
       <c r="CL22" s="2"/>
       <c r="CM22" s="2"/>
@@ -2598,91 +2894,91 @@
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="1"/>
-      <c r="AI23" s="1"/>
-      <c r="AJ23" s="1"/>
-      <c r="AK23" s="5"/>
-      <c r="AL23" s="5"/>
-      <c r="AM23" s="5"/>
-      <c r="AN23" s="1"/>
-      <c r="AO23" s="1"/>
-      <c r="AP23" s="1"/>
-      <c r="AQ23" s="1"/>
-      <c r="AR23" s="1"/>
-      <c r="AS23" s="1"/>
-      <c r="AT23" s="1"/>
-      <c r="AU23" s="1"/>
-      <c r="AV23" s="1"/>
-      <c r="AW23" s="1"/>
-      <c r="AX23" s="1"/>
-      <c r="AY23" s="1"/>
-      <c r="AZ23" s="1"/>
-      <c r="BA23" s="5"/>
-      <c r="BB23" s="5"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="1"/>
-      <c r="BE23" s="1"/>
-      <c r="BF23" s="1"/>
-      <c r="BG23" s="1"/>
-      <c r="BH23" s="5"/>
-      <c r="BI23" s="1"/>
-      <c r="BJ23" s="1"/>
-      <c r="BK23" s="1"/>
-      <c r="BL23" s="5"/>
-      <c r="BM23" s="1"/>
-      <c r="BN23" s="1"/>
-      <c r="BO23" s="1"/>
-      <c r="BP23" s="1"/>
-      <c r="BQ23" s="5"/>
-      <c r="BR23" s="1"/>
-      <c r="BS23" s="5"/>
-      <c r="BT23" s="5"/>
-      <c r="BU23" s="5"/>
-      <c r="BV23" s="5"/>
-      <c r="BW23" s="5"/>
-      <c r="BX23" s="5"/>
-      <c r="BY23" s="5"/>
-      <c r="BZ23" s="5"/>
-      <c r="CA23" s="5"/>
-      <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
-      <c r="CD23" s="5"/>
-      <c r="CE23" s="5"/>
-      <c r="CF23" s="5"/>
-      <c r="CG23" s="5"/>
-      <c r="CH23" s="5"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="4"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="2"/>
+      <c r="AM23" s="2"/>
+      <c r="AN23" s="2"/>
+      <c r="AO23" s="2"/>
+      <c r="AP23" s="2"/>
+      <c r="AQ23" s="2"/>
+      <c r="AR23" s="2"/>
+      <c r="AS23" s="2"/>
+      <c r="AT23" s="2"/>
+      <c r="AU23" s="2"/>
+      <c r="AV23" s="2"/>
+      <c r="AW23" s="2"/>
+      <c r="AX23" s="2"/>
+      <c r="AY23" s="2"/>
+      <c r="AZ23" s="2"/>
+      <c r="BA23" s="2"/>
+      <c r="BB23" s="2"/>
+      <c r="BC23" s="2"/>
+      <c r="BD23" s="2"/>
+      <c r="BE23" s="2"/>
+      <c r="BF23" s="2"/>
+      <c r="BG23" s="2"/>
+      <c r="BH23" s="2"/>
+      <c r="BI23" s="2"/>
+      <c r="BJ23" s="2"/>
+      <c r="BK23" s="2"/>
+      <c r="BL23" s="2"/>
+      <c r="BM23" s="2"/>
+      <c r="BN23" s="2"/>
+      <c r="BO23" s="2"/>
+      <c r="BP23" s="2"/>
+      <c r="BQ23" s="2"/>
+      <c r="BR23" s="2"/>
+      <c r="BS23" s="2"/>
+      <c r="BT23" s="2"/>
+      <c r="BU23" s="2"/>
+      <c r="BV23" s="2"/>
+      <c r="BW23" s="2"/>
+      <c r="BX23" s="2"/>
+      <c r="BY23" s="2"/>
+      <c r="BZ23" s="2"/>
+      <c r="CA23" s="2"/>
+      <c r="CB23" s="2"/>
+      <c r="CC23" s="2"/>
+      <c r="CD23" s="2"/>
+      <c r="CE23" s="2"/>
+      <c r="CF23" s="2"/>
+      <c r="CG23" s="2"/>
+      <c r="CH23" s="2"/>
+      <c r="CI23" s="2"/>
+      <c r="CJ23" s="2"/>
       <c r="CK23" s="2"/>
       <c r="CL23" s="2"/>
       <c r="CM23" s="2"/>
@@ -2693,91 +2989,91 @@
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
-      <c r="AH24" s="1"/>
-      <c r="AI24" s="1"/>
-      <c r="AJ24" s="1"/>
-      <c r="AK24" s="5"/>
-      <c r="AL24" s="5"/>
-      <c r="AM24" s="5"/>
-      <c r="AN24" s="1"/>
-      <c r="AO24" s="1"/>
-      <c r="AP24" s="1"/>
-      <c r="AQ24" s="1"/>
-      <c r="AR24" s="1"/>
-      <c r="AS24" s="1"/>
-      <c r="AT24" s="1"/>
-      <c r="AU24" s="1"/>
-      <c r="AV24" s="1"/>
-      <c r="AW24" s="1"/>
-      <c r="AX24" s="1"/>
-      <c r="AY24" s="1"/>
-      <c r="AZ24" s="1"/>
-      <c r="BA24" s="5"/>
-      <c r="BB24" s="5"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="1"/>
-      <c r="BE24" s="1"/>
-      <c r="BF24" s="1"/>
-      <c r="BG24" s="1"/>
-      <c r="BH24" s="5"/>
-      <c r="BI24" s="1"/>
-      <c r="BJ24" s="1"/>
-      <c r="BK24" s="1"/>
-      <c r="BL24" s="5"/>
-      <c r="BM24" s="1"/>
-      <c r="BN24" s="1"/>
-      <c r="BO24" s="1"/>
-      <c r="BP24" s="1"/>
-      <c r="BQ24" s="5"/>
-      <c r="BR24" s="1"/>
-      <c r="BS24" s="1"/>
-      <c r="BT24" s="1"/>
-      <c r="BU24" s="5"/>
-      <c r="BV24" s="1"/>
-      <c r="BW24" s="1"/>
-      <c r="BX24" s="1"/>
-      <c r="BY24" s="1"/>
-      <c r="BZ24" s="5"/>
-      <c r="CA24" s="1"/>
-      <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
-      <c r="CD24" s="5"/>
-      <c r="CE24" s="5"/>
-      <c r="CF24" s="5"/>
-      <c r="CG24" s="5"/>
-      <c r="CH24" s="5"/>
-      <c r="CI24" s="5"/>
-      <c r="CJ24" s="4"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="2"/>
+      <c r="AM24" s="2"/>
+      <c r="AN24" s="2"/>
+      <c r="AO24" s="2"/>
+      <c r="AP24" s="2"/>
+      <c r="AQ24" s="2"/>
+      <c r="AR24" s="2"/>
+      <c r="AS24" s="2"/>
+      <c r="AT24" s="2"/>
+      <c r="AU24" s="2"/>
+      <c r="AV24" s="2"/>
+      <c r="AW24" s="2"/>
+      <c r="AX24" s="2"/>
+      <c r="AY24" s="2"/>
+      <c r="AZ24" s="2"/>
+      <c r="BA24" s="2"/>
+      <c r="BB24" s="2"/>
+      <c r="BC24" s="2"/>
+      <c r="BD24" s="2"/>
+      <c r="BE24" s="2"/>
+      <c r="BF24" s="2"/>
+      <c r="BG24" s="2"/>
+      <c r="BH24" s="2"/>
+      <c r="BI24" s="2"/>
+      <c r="BJ24" s="2"/>
+      <c r="BK24" s="2"/>
+      <c r="BL24" s="2"/>
+      <c r="BM24" s="2"/>
+      <c r="BN24" s="2"/>
+      <c r="BO24" s="2"/>
+      <c r="BP24" s="2"/>
+      <c r="BQ24" s="2"/>
+      <c r="BR24" s="2"/>
+      <c r="BS24" s="2"/>
+      <c r="BT24" s="2"/>
+      <c r="BU24" s="2"/>
+      <c r="BV24" s="2"/>
+      <c r="BW24" s="2"/>
+      <c r="BX24" s="2"/>
+      <c r="BY24" s="2"/>
+      <c r="BZ24" s="2"/>
+      <c r="CA24" s="2"/>
+      <c r="CB24" s="2"/>
+      <c r="CC24" s="2"/>
+      <c r="CD24" s="2"/>
+      <c r="CE24" s="2"/>
+      <c r="CF24" s="2"/>
+      <c r="CG24" s="2"/>
+      <c r="CH24" s="2"/>
+      <c r="CI24" s="2"/>
+      <c r="CJ24" s="2"/>
       <c r="CK24" s="2"/>
       <c r="CL24" s="2"/>
       <c r="CM24" s="2"/>
@@ -2788,92 +3084,92 @@
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
-      <c r="AG25" s="1"/>
-      <c r="AH25" s="1"/>
-      <c r="AI25" s="1"/>
-      <c r="AJ25" s="1"/>
-      <c r="AK25" s="5"/>
-      <c r="AL25" s="5"/>
-      <c r="AM25" s="5"/>
-      <c r="AN25" s="1"/>
-      <c r="AO25" s="1"/>
-      <c r="AP25" s="1"/>
-      <c r="AQ25" s="1"/>
-      <c r="AR25" s="1"/>
-      <c r="AS25" s="1"/>
-      <c r="AT25" s="1"/>
-      <c r="AU25" s="1"/>
-      <c r="AV25" s="1"/>
-      <c r="AW25" s="1"/>
-      <c r="AX25" s="1"/>
-      <c r="AY25" s="1"/>
-      <c r="AZ25" s="1"/>
-      <c r="BA25" s="5"/>
-      <c r="BB25" s="5"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="1"/>
-      <c r="BE25" s="1"/>
-      <c r="BF25" s="1"/>
-      <c r="BG25" s="1"/>
-      <c r="BH25" s="5"/>
-      <c r="BI25" s="1"/>
-      <c r="BJ25" s="1"/>
-      <c r="BK25" s="1"/>
-      <c r="BL25" s="5"/>
-      <c r="BM25" s="1"/>
-      <c r="BN25" s="1"/>
-      <c r="BO25" s="1"/>
-      <c r="BP25" s="1"/>
-      <c r="BQ25" s="5"/>
-      <c r="BR25" s="1"/>
-      <c r="BS25" s="1"/>
-      <c r="BT25" s="1"/>
-      <c r="BU25" s="5"/>
-      <c r="BV25" s="1"/>
-      <c r="BW25" s="1"/>
-      <c r="BX25" s="1"/>
-      <c r="BY25" s="1"/>
-      <c r="BZ25" s="5"/>
-      <c r="CA25" s="1"/>
-      <c r="CB25" s="1"/>
-      <c r="CC25" s="1"/>
-      <c r="CD25" s="5"/>
-      <c r="CE25" s="1"/>
-      <c r="CF25" s="5"/>
-      <c r="CG25" s="5"/>
-      <c r="CH25" s="5"/>
-      <c r="CI25" s="5"/>
-      <c r="CJ25" s="4"/>
-      <c r="CK25" s="4"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
+      <c r="AH25" s="2"/>
+      <c r="AI25" s="2"/>
+      <c r="AJ25" s="2"/>
+      <c r="AK25" s="2"/>
+      <c r="AL25" s="2"/>
+      <c r="AM25" s="2"/>
+      <c r="AN25" s="2"/>
+      <c r="AO25" s="2"/>
+      <c r="AP25" s="2"/>
+      <c r="AQ25" s="2"/>
+      <c r="AR25" s="2"/>
+      <c r="AS25" s="2"/>
+      <c r="AT25" s="2"/>
+      <c r="AU25" s="2"/>
+      <c r="AV25" s="2"/>
+      <c r="AW25" s="2"/>
+      <c r="AX25" s="2"/>
+      <c r="AY25" s="2"/>
+      <c r="AZ25" s="2"/>
+      <c r="BA25" s="2"/>
+      <c r="BB25" s="2"/>
+      <c r="BC25" s="2"/>
+      <c r="BD25" s="2"/>
+      <c r="BE25" s="2"/>
+      <c r="BF25" s="2"/>
+      <c r="BG25" s="2"/>
+      <c r="BH25" s="2"/>
+      <c r="BI25" s="2"/>
+      <c r="BJ25" s="2"/>
+      <c r="BK25" s="2"/>
+      <c r="BL25" s="2"/>
+      <c r="BM25" s="2"/>
+      <c r="BN25" s="2"/>
+      <c r="BO25" s="2"/>
+      <c r="BP25" s="2"/>
+      <c r="BQ25" s="2"/>
+      <c r="BR25" s="2"/>
+      <c r="BS25" s="2"/>
+      <c r="BT25" s="2"/>
+      <c r="BU25" s="2"/>
+      <c r="BV25" s="2"/>
+      <c r="BW25" s="2"/>
+      <c r="BX25" s="2"/>
+      <c r="BY25" s="2"/>
+      <c r="BZ25" s="2"/>
+      <c r="CA25" s="2"/>
+      <c r="CB25" s="2"/>
+      <c r="CC25" s="2"/>
+      <c r="CD25" s="2"/>
+      <c r="CE25" s="2"/>
+      <c r="CF25" s="2"/>
+      <c r="CG25" s="2"/>
+      <c r="CH25" s="2"/>
+      <c r="CI25" s="2"/>
+      <c r="CJ25" s="2"/>
+      <c r="CK25" s="2"/>
       <c r="CL25" s="2"/>
       <c r="CM25" s="2"/>
       <c r="CN25" s="2"/>
@@ -2883,92 +3179,92 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1"/>
-      <c r="AG26" s="1"/>
-      <c r="AH26" s="1"/>
-      <c r="AI26" s="1"/>
-      <c r="AJ26" s="1"/>
-      <c r="AK26" s="5"/>
-      <c r="AL26" s="5"/>
-      <c r="AM26" s="5"/>
-      <c r="AN26" s="1"/>
-      <c r="AO26" s="1"/>
-      <c r="AP26" s="1"/>
-      <c r="AQ26" s="1"/>
-      <c r="AR26" s="1"/>
-      <c r="AS26" s="1"/>
-      <c r="AT26" s="1"/>
-      <c r="AU26" s="1"/>
-      <c r="AV26" s="1"/>
-      <c r="AW26" s="1"/>
-      <c r="AX26" s="1"/>
-      <c r="AY26" s="1"/>
-      <c r="AZ26" s="1"/>
-      <c r="BA26" s="5"/>
-      <c r="BB26" s="5"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="5"/>
-      <c r="BE26" s="5"/>
-      <c r="BF26" s="5"/>
-      <c r="BG26" s="5"/>
-      <c r="BH26" s="5"/>
-      <c r="BI26" s="5"/>
-      <c r="BJ26" s="5"/>
-      <c r="BK26" s="1"/>
-      <c r="BL26" s="5"/>
-      <c r="BM26" s="1"/>
-      <c r="BN26" s="1"/>
-      <c r="BO26" s="1"/>
-      <c r="BP26" s="1"/>
-      <c r="BQ26" s="5"/>
-      <c r="BR26" s="1"/>
-      <c r="BS26" s="1"/>
-      <c r="BT26" s="1"/>
-      <c r="BU26" s="5"/>
-      <c r="BV26" s="1"/>
-      <c r="BW26" s="1"/>
-      <c r="BX26" s="1"/>
-      <c r="BY26" s="1"/>
-      <c r="BZ26" s="5"/>
-      <c r="CA26" s="1"/>
-      <c r="CB26" s="1"/>
-      <c r="CC26" s="1"/>
-      <c r="CD26" s="5"/>
-      <c r="CE26" s="1"/>
-      <c r="CF26" s="1"/>
-      <c r="CG26" s="1"/>
-      <c r="CH26" s="5"/>
-      <c r="CI26" s="5"/>
-      <c r="CJ26" s="5"/>
-      <c r="CK26" s="4"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="2"/>
+      <c r="AL26" s="2"/>
+      <c r="AM26" s="2"/>
+      <c r="AN26" s="2"/>
+      <c r="AO26" s="2"/>
+      <c r="AP26" s="2"/>
+      <c r="AQ26" s="2"/>
+      <c r="AR26" s="2"/>
+      <c r="AS26" s="2"/>
+      <c r="AT26" s="2"/>
+      <c r="AU26" s="2"/>
+      <c r="AV26" s="2"/>
+      <c r="AW26" s="2"/>
+      <c r="AX26" s="2"/>
+      <c r="AY26" s="2"/>
+      <c r="AZ26" s="2"/>
+      <c r="BA26" s="2"/>
+      <c r="BB26" s="2"/>
+      <c r="BC26" s="2"/>
+      <c r="BD26" s="2"/>
+      <c r="BE26" s="2"/>
+      <c r="BF26" s="2"/>
+      <c r="BG26" s="2"/>
+      <c r="BH26" s="2"/>
+      <c r="BI26" s="2"/>
+      <c r="BJ26" s="2"/>
+      <c r="BK26" s="2"/>
+      <c r="BL26" s="2"/>
+      <c r="BM26" s="2"/>
+      <c r="BN26" s="2"/>
+      <c r="BO26" s="2"/>
+      <c r="BP26" s="2"/>
+      <c r="BQ26" s="2"/>
+      <c r="BR26" s="2"/>
+      <c r="BS26" s="2"/>
+      <c r="BT26" s="2"/>
+      <c r="BU26" s="2"/>
+      <c r="BV26" s="2"/>
+      <c r="BW26" s="2"/>
+      <c r="BX26" s="2"/>
+      <c r="BY26" s="2"/>
+      <c r="BZ26" s="2"/>
+      <c r="CA26" s="2"/>
+      <c r="CB26" s="2"/>
+      <c r="CC26" s="2"/>
+      <c r="CD26" s="2"/>
+      <c r="CE26" s="2"/>
+      <c r="CF26" s="2"/>
+      <c r="CG26" s="2"/>
+      <c r="CH26" s="2"/>
+      <c r="CI26" s="2"/>
+      <c r="CJ26" s="2"/>
+      <c r="CK26" s="2"/>
       <c r="CL26" s="2"/>
       <c r="CM26" s="2"/>
       <c r="CN26" s="2"/>
@@ -2978,92 +3274,92 @@
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
-      <c r="AF27" s="1"/>
-      <c r="AG27" s="1"/>
-      <c r="AH27" s="1"/>
-      <c r="AI27" s="1"/>
-      <c r="AJ27" s="1"/>
-      <c r="AK27" s="5"/>
-      <c r="AL27" s="5"/>
-      <c r="AM27" s="5"/>
-      <c r="AN27" s="1"/>
-      <c r="AO27" s="1"/>
-      <c r="AP27" s="1"/>
-      <c r="AQ27" s="1"/>
-      <c r="AR27" s="1"/>
-      <c r="AS27" s="1"/>
-      <c r="AT27" s="1"/>
-      <c r="AU27" s="1"/>
-      <c r="AV27" s="1"/>
-      <c r="AW27" s="1"/>
-      <c r="AX27" s="1"/>
-      <c r="AY27" s="1"/>
-      <c r="AZ27" s="1"/>
-      <c r="BA27" s="5"/>
-      <c r="BB27" s="5"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="1"/>
-      <c r="BE27" s="1"/>
-      <c r="BF27" s="1"/>
-      <c r="BG27" s="1"/>
-      <c r="BH27" s="5"/>
-      <c r="BI27" s="1"/>
-      <c r="BJ27" s="1"/>
-      <c r="BK27" s="5"/>
-      <c r="BL27" s="5"/>
-      <c r="BM27" s="5"/>
-      <c r="BN27" s="1"/>
-      <c r="BO27" s="1"/>
-      <c r="BP27" s="1"/>
-      <c r="BQ27" s="5"/>
-      <c r="BR27" s="1"/>
-      <c r="BS27" s="1"/>
-      <c r="BT27" s="1"/>
-      <c r="BU27" s="5"/>
-      <c r="BV27" s="5"/>
-      <c r="BW27" s="5"/>
-      <c r="BX27" s="5"/>
-      <c r="BY27" s="5"/>
-      <c r="BZ27" s="5"/>
-      <c r="CA27" s="5"/>
-      <c r="CB27" s="5"/>
-      <c r="CC27" s="5"/>
-      <c r="CD27" s="5"/>
-      <c r="CE27" s="1"/>
-      <c r="CF27" s="1"/>
-      <c r="CG27" s="1"/>
-      <c r="CH27" s="5"/>
-      <c r="CI27" s="5"/>
-      <c r="CJ27" s="5"/>
-      <c r="CK27" s="4"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+      <c r="AL27" s="2"/>
+      <c r="AM27" s="2"/>
+      <c r="AN27" s="2"/>
+      <c r="AO27" s="2"/>
+      <c r="AP27" s="2"/>
+      <c r="AQ27" s="2"/>
+      <c r="AR27" s="2"/>
+      <c r="AS27" s="2"/>
+      <c r="AT27" s="2"/>
+      <c r="AU27" s="2"/>
+      <c r="AV27" s="2"/>
+      <c r="AW27" s="2"/>
+      <c r="AX27" s="2"/>
+      <c r="AY27" s="2"/>
+      <c r="AZ27" s="2"/>
+      <c r="BA27" s="2"/>
+      <c r="BB27" s="2"/>
+      <c r="BC27" s="2"/>
+      <c r="BD27" s="2"/>
+      <c r="BE27" s="2"/>
+      <c r="BF27" s="2"/>
+      <c r="BG27" s="2"/>
+      <c r="BH27" s="2"/>
+      <c r="BI27" s="2"/>
+      <c r="BJ27" s="2"/>
+      <c r="BK27" s="2"/>
+      <c r="BL27" s="2"/>
+      <c r="BM27" s="2"/>
+      <c r="BN27" s="2"/>
+      <c r="BO27" s="2"/>
+      <c r="BP27" s="2"/>
+      <c r="BQ27" s="2"/>
+      <c r="BR27" s="2"/>
+      <c r="BS27" s="2"/>
+      <c r="BT27" s="2"/>
+      <c r="BU27" s="2"/>
+      <c r="BV27" s="2"/>
+      <c r="BW27" s="2"/>
+      <c r="BX27" s="2"/>
+      <c r="BY27" s="2"/>
+      <c r="BZ27" s="2"/>
+      <c r="CA27" s="2"/>
+      <c r="CB27" s="2"/>
+      <c r="CC27" s="2"/>
+      <c r="CD27" s="2"/>
+      <c r="CE27" s="2"/>
+      <c r="CF27" s="2"/>
+      <c r="CG27" s="2"/>
+      <c r="CH27" s="2"/>
+      <c r="CI27" s="2"/>
+      <c r="CJ27" s="2"/>
+      <c r="CK27" s="2"/>
       <c r="CL27" s="2"/>
       <c r="CM27" s="2"/>
       <c r="CN27" s="2"/>
@@ -3073,92 +3369,92 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
-      <c r="AH28" s="1"/>
-      <c r="AI28" s="1"/>
-      <c r="AJ28" s="1"/>
-      <c r="AK28" s="5"/>
-      <c r="AL28" s="5"/>
-      <c r="AM28" s="5"/>
-      <c r="AN28" s="1"/>
-      <c r="AO28" s="1"/>
-      <c r="AP28" s="1"/>
-      <c r="AQ28" s="1"/>
-      <c r="AR28" s="1"/>
-      <c r="AS28" s="1"/>
-      <c r="AT28" s="1"/>
-      <c r="AU28" s="1"/>
-      <c r="AV28" s="1"/>
-      <c r="AW28" s="1"/>
-      <c r="AX28" s="1"/>
-      <c r="AY28" s="1"/>
-      <c r="AZ28" s="1"/>
-      <c r="BA28" s="5"/>
-      <c r="BB28" s="5"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="1"/>
-      <c r="BE28" s="1"/>
-      <c r="BF28" s="1"/>
-      <c r="BG28" s="1"/>
-      <c r="BH28" s="5"/>
-      <c r="BI28" s="1"/>
-      <c r="BJ28" s="1"/>
-      <c r="BK28" s="1"/>
-      <c r="BL28" s="5"/>
-      <c r="BM28" s="1"/>
-      <c r="BN28" s="5"/>
-      <c r="BO28" s="5"/>
-      <c r="BP28" s="1"/>
-      <c r="BQ28" s="5"/>
-      <c r="BR28" s="1"/>
-      <c r="BS28" s="1"/>
-      <c r="BT28" s="1"/>
-      <c r="BU28" s="5"/>
-      <c r="BV28" s="1"/>
-      <c r="BW28" s="1"/>
-      <c r="BX28" s="1"/>
-      <c r="BY28" s="1"/>
-      <c r="BZ28" s="5"/>
-      <c r="CA28" s="1"/>
-      <c r="CB28" s="1"/>
-      <c r="CC28" s="1"/>
-      <c r="CD28" s="5"/>
-      <c r="CE28" s="1"/>
-      <c r="CF28" s="1"/>
-      <c r="CG28" s="1"/>
-      <c r="CH28" s="5"/>
-      <c r="CI28" s="5"/>
-      <c r="CJ28" s="5"/>
-      <c r="CK28" s="4"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
+      <c r="AM28" s="2"/>
+      <c r="AN28" s="2"/>
+      <c r="AO28" s="2"/>
+      <c r="AP28" s="2"/>
+      <c r="AQ28" s="2"/>
+      <c r="AR28" s="2"/>
+      <c r="AS28" s="2"/>
+      <c r="AT28" s="2"/>
+      <c r="AU28" s="2"/>
+      <c r="AV28" s="2"/>
+      <c r="AW28" s="2"/>
+      <c r="AX28" s="2"/>
+      <c r="AY28" s="2"/>
+      <c r="AZ28" s="2"/>
+      <c r="BA28" s="2"/>
+      <c r="BB28" s="2"/>
+      <c r="BC28" s="2"/>
+      <c r="BD28" s="2"/>
+      <c r="BE28" s="2"/>
+      <c r="BF28" s="2"/>
+      <c r="BG28" s="2"/>
+      <c r="BH28" s="2"/>
+      <c r="BI28" s="2"/>
+      <c r="BJ28" s="2"/>
+      <c r="BK28" s="2"/>
+      <c r="BL28" s="2"/>
+      <c r="BM28" s="2"/>
+      <c r="BN28" s="2"/>
+      <c r="BO28" s="2"/>
+      <c r="BP28" s="2"/>
+      <c r="BQ28" s="2"/>
+      <c r="BR28" s="2"/>
+      <c r="BS28" s="2"/>
+      <c r="BT28" s="2"/>
+      <c r="BU28" s="2"/>
+      <c r="BV28" s="2"/>
+      <c r="BW28" s="2"/>
+      <c r="BX28" s="2"/>
+      <c r="BY28" s="2"/>
+      <c r="BZ28" s="2"/>
+      <c r="CA28" s="2"/>
+      <c r="CB28" s="2"/>
+      <c r="CC28" s="2"/>
+      <c r="CD28" s="2"/>
+      <c r="CE28" s="2"/>
+      <c r="CF28" s="2"/>
+      <c r="CG28" s="2"/>
+      <c r="CH28" s="2"/>
+      <c r="CI28" s="2"/>
+      <c r="CJ28" s="2"/>
+      <c r="CK28" s="2"/>
       <c r="CL28" s="2"/>
       <c r="CM28" s="2"/>
       <c r="CN28" s="2"/>
@@ -3168,92 +3464,92 @@
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
-      <c r="AF29" s="1"/>
-      <c r="AG29" s="1"/>
-      <c r="AH29" s="1"/>
-      <c r="AI29" s="1"/>
-      <c r="AJ29" s="1"/>
-      <c r="AK29" s="5"/>
-      <c r="AL29" s="5"/>
-      <c r="AM29" s="5"/>
-      <c r="AN29" s="1"/>
-      <c r="AO29" s="1"/>
-      <c r="AP29" s="1"/>
-      <c r="AQ29" s="1"/>
-      <c r="AR29" s="1"/>
-      <c r="AS29" s="1"/>
-      <c r="AT29" s="1"/>
-      <c r="AU29" s="1"/>
-      <c r="AV29" s="1"/>
-      <c r="AW29" s="1"/>
-      <c r="AX29" s="1"/>
-      <c r="AY29" s="1"/>
-      <c r="AZ29" s="1"/>
-      <c r="BA29" s="5"/>
-      <c r="BB29" s="5"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="1"/>
-      <c r="BE29" s="1"/>
-      <c r="BF29" s="1"/>
-      <c r="BG29" s="1"/>
-      <c r="BH29" s="5"/>
-      <c r="BI29" s="1"/>
-      <c r="BJ29" s="1"/>
-      <c r="BK29" s="1"/>
-      <c r="BL29" s="5"/>
-      <c r="BM29" s="1"/>
-      <c r="BN29" s="1"/>
-      <c r="BO29" s="1"/>
-      <c r="BP29" s="5"/>
-      <c r="BQ29" s="5"/>
-      <c r="BR29" s="5"/>
-      <c r="BS29" s="1"/>
-      <c r="BT29" s="1"/>
-      <c r="BU29" s="5"/>
-      <c r="BV29" s="1"/>
-      <c r="BW29" s="1"/>
-      <c r="BX29" s="1"/>
-      <c r="BY29" s="1"/>
-      <c r="BZ29" s="5"/>
-      <c r="CA29" s="1"/>
-      <c r="CB29" s="1"/>
-      <c r="CC29" s="1"/>
-      <c r="CD29" s="5"/>
-      <c r="CE29" s="1"/>
-      <c r="CF29" s="1"/>
-      <c r="CG29" s="1"/>
-      <c r="CH29" s="5"/>
-      <c r="CI29" s="5"/>
-      <c r="CJ29" s="5"/>
-      <c r="CK29" s="4"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+      <c r="AF29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+      <c r="AL29" s="2"/>
+      <c r="AM29" s="2"/>
+      <c r="AN29" s="2"/>
+      <c r="AO29" s="2"/>
+      <c r="AP29" s="2"/>
+      <c r="AQ29" s="2"/>
+      <c r="AR29" s="2"/>
+      <c r="AS29" s="2"/>
+      <c r="AT29" s="2"/>
+      <c r="AU29" s="2"/>
+      <c r="AV29" s="2"/>
+      <c r="AW29" s="2"/>
+      <c r="AX29" s="2"/>
+      <c r="AY29" s="2"/>
+      <c r="AZ29" s="2"/>
+      <c r="BA29" s="2"/>
+      <c r="BB29" s="2"/>
+      <c r="BC29" s="2"/>
+      <c r="BD29" s="2"/>
+      <c r="BE29" s="2"/>
+      <c r="BF29" s="2"/>
+      <c r="BG29" s="2"/>
+      <c r="BH29" s="2"/>
+      <c r="BI29" s="2"/>
+      <c r="BJ29" s="2"/>
+      <c r="BK29" s="2"/>
+      <c r="BL29" s="2"/>
+      <c r="BM29" s="2"/>
+      <c r="BN29" s="2"/>
+      <c r="BO29" s="2"/>
+      <c r="BP29" s="2"/>
+      <c r="BQ29" s="2"/>
+      <c r="BR29" s="2"/>
+      <c r="BS29" s="2"/>
+      <c r="BT29" s="2"/>
+      <c r="BU29" s="2"/>
+      <c r="BV29" s="2"/>
+      <c r="BW29" s="2"/>
+      <c r="BX29" s="2"/>
+      <c r="BY29" s="2"/>
+      <c r="BZ29" s="2"/>
+      <c r="CA29" s="2"/>
+      <c r="CB29" s="2"/>
+      <c r="CC29" s="2"/>
+      <c r="CD29" s="2"/>
+      <c r="CE29" s="2"/>
+      <c r="CF29" s="2"/>
+      <c r="CG29" s="2"/>
+      <c r="CH29" s="2"/>
+      <c r="CI29" s="2"/>
+      <c r="CJ29" s="2"/>
+      <c r="CK29" s="2"/>
       <c r="CL29" s="2"/>
       <c r="CM29" s="2"/>
       <c r="CN29" s="2"/>
@@ -3263,92 +3559,92 @@
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-      <c r="AH30" s="1"/>
-      <c r="AI30" s="1"/>
-      <c r="AJ30" s="1"/>
-      <c r="AK30" s="5"/>
-      <c r="AL30" s="5"/>
-      <c r="AM30" s="5"/>
-      <c r="AN30" s="1"/>
-      <c r="AO30" s="1"/>
-      <c r="AP30" s="1"/>
-      <c r="AQ30" s="1"/>
-      <c r="AR30" s="1"/>
-      <c r="AS30" s="1"/>
-      <c r="AT30" s="1"/>
-      <c r="AU30" s="1"/>
-      <c r="AV30" s="1"/>
-      <c r="AW30" s="1"/>
-      <c r="AX30" s="1"/>
-      <c r="AY30" s="1"/>
-      <c r="AZ30" s="1"/>
-      <c r="BA30" s="5"/>
-      <c r="BB30" s="5"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="1"/>
-      <c r="BE30" s="1"/>
-      <c r="BF30" s="1"/>
-      <c r="BG30" s="1"/>
-      <c r="BH30" s="5"/>
-      <c r="BI30" s="1"/>
-      <c r="BJ30" s="1"/>
-      <c r="BK30" s="1"/>
-      <c r="BL30" s="5"/>
-      <c r="BM30" s="1"/>
-      <c r="BN30" s="1"/>
-      <c r="BO30" s="1"/>
-      <c r="BP30" s="1"/>
-      <c r="BQ30" s="5"/>
-      <c r="BR30" s="1"/>
-      <c r="BS30" s="5"/>
-      <c r="BT30" s="5"/>
-      <c r="BU30" s="5"/>
-      <c r="BV30" s="5"/>
-      <c r="BW30" s="1"/>
-      <c r="BX30" s="1"/>
-      <c r="BY30" s="1"/>
-      <c r="BZ30" s="5"/>
-      <c r="CA30" s="1"/>
-      <c r="CB30" s="1"/>
-      <c r="CC30" s="1"/>
-      <c r="CD30" s="5"/>
-      <c r="CE30" s="5"/>
-      <c r="CF30" s="5"/>
-      <c r="CG30" s="5"/>
-      <c r="CH30" s="5"/>
-      <c r="CI30" s="5"/>
-      <c r="CJ30" s="5"/>
-      <c r="CK30" s="4"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2"/>
+      <c r="AF30" s="2"/>
+      <c r="AG30" s="2"/>
+      <c r="AH30" s="2"/>
+      <c r="AI30" s="2"/>
+      <c r="AJ30" s="2"/>
+      <c r="AK30" s="2"/>
+      <c r="AL30" s="2"/>
+      <c r="AM30" s="2"/>
+      <c r="AN30" s="2"/>
+      <c r="AO30" s="2"/>
+      <c r="AP30" s="2"/>
+      <c r="AQ30" s="2"/>
+      <c r="AR30" s="2"/>
+      <c r="AS30" s="2"/>
+      <c r="AT30" s="2"/>
+      <c r="AU30" s="2"/>
+      <c r="AV30" s="2"/>
+      <c r="AW30" s="2"/>
+      <c r="AX30" s="2"/>
+      <c r="AY30" s="2"/>
+      <c r="AZ30" s="2"/>
+      <c r="BA30" s="2"/>
+      <c r="BB30" s="2"/>
+      <c r="BC30" s="2"/>
+      <c r="BD30" s="2"/>
+      <c r="BE30" s="2"/>
+      <c r="BF30" s="2"/>
+      <c r="BG30" s="2"/>
+      <c r="BH30" s="2"/>
+      <c r="BI30" s="2"/>
+      <c r="BJ30" s="2"/>
+      <c r="BK30" s="2"/>
+      <c r="BL30" s="2"/>
+      <c r="BM30" s="2"/>
+      <c r="BN30" s="2"/>
+      <c r="BO30" s="2"/>
+      <c r="BP30" s="2"/>
+      <c r="BQ30" s="2"/>
+      <c r="BR30" s="2"/>
+      <c r="BS30" s="2"/>
+      <c r="BT30" s="2"/>
+      <c r="BU30" s="2"/>
+      <c r="BV30" s="2"/>
+      <c r="BW30" s="2"/>
+      <c r="BX30" s="2"/>
+      <c r="BY30" s="2"/>
+      <c r="BZ30" s="2"/>
+      <c r="CA30" s="2"/>
+      <c r="CB30" s="2"/>
+      <c r="CC30" s="2"/>
+      <c r="CD30" s="2"/>
+      <c r="CE30" s="2"/>
+      <c r="CF30" s="2"/>
+      <c r="CG30" s="2"/>
+      <c r="CH30" s="2"/>
+      <c r="CI30" s="2"/>
+      <c r="CJ30" s="2"/>
+      <c r="CK30" s="2"/>
       <c r="CL30" s="2"/>
       <c r="CM30" s="2"/>
       <c r="CN30" s="2"/>
@@ -3358,92 +3654,92 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
-      <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
-      <c r="AH31" s="1"/>
-      <c r="AI31" s="1"/>
-      <c r="AJ31" s="1"/>
-      <c r="AK31" s="5"/>
-      <c r="AL31" s="5"/>
-      <c r="AM31" s="5"/>
-      <c r="AN31" s="1"/>
-      <c r="AO31" s="1"/>
-      <c r="AP31" s="1"/>
-      <c r="AQ31" s="1"/>
-      <c r="AR31" s="1"/>
-      <c r="AS31" s="1"/>
-      <c r="AT31" s="1"/>
-      <c r="AU31" s="1"/>
-      <c r="AV31" s="1"/>
-      <c r="AW31" s="1"/>
-      <c r="AX31" s="1"/>
-      <c r="AY31" s="1"/>
-      <c r="AZ31" s="1"/>
-      <c r="BA31" s="5"/>
-      <c r="BB31" s="5"/>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="1"/>
-      <c r="BE31" s="1"/>
-      <c r="BF31" s="1"/>
-      <c r="BG31" s="1"/>
-      <c r="BH31" s="5"/>
-      <c r="BI31" s="1"/>
-      <c r="BJ31" s="1"/>
-      <c r="BK31" s="1"/>
-      <c r="BL31" s="5"/>
-      <c r="BM31" s="1"/>
-      <c r="BN31" s="1"/>
-      <c r="BO31" s="1"/>
-      <c r="BP31" s="1"/>
-      <c r="BQ31" s="5"/>
-      <c r="BR31" s="1"/>
-      <c r="BS31" s="1"/>
-      <c r="BT31" s="1"/>
-      <c r="BU31" s="5"/>
-      <c r="BV31" s="1"/>
-      <c r="BW31" s="5"/>
-      <c r="BX31" s="1"/>
-      <c r="BY31" s="1"/>
-      <c r="BZ31" s="5"/>
-      <c r="CA31" s="1"/>
-      <c r="CB31" s="1"/>
-      <c r="CC31" s="1"/>
-      <c r="CD31" s="5"/>
-      <c r="CE31" s="1"/>
-      <c r="CF31" s="1"/>
-      <c r="CG31" s="1"/>
-      <c r="CH31" s="5"/>
-      <c r="CI31" s="5"/>
-      <c r="CJ31" s="5"/>
-      <c r="CK31" s="4"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+      <c r="AF31" s="2"/>
+      <c r="AG31" s="2"/>
+      <c r="AH31" s="2"/>
+      <c r="AI31" s="2"/>
+      <c r="AJ31" s="2"/>
+      <c r="AK31" s="2"/>
+      <c r="AL31" s="2"/>
+      <c r="AM31" s="2"/>
+      <c r="AN31" s="2"/>
+      <c r="AO31" s="2"/>
+      <c r="AP31" s="2"/>
+      <c r="AQ31" s="2"/>
+      <c r="AR31" s="2"/>
+      <c r="AS31" s="2"/>
+      <c r="AT31" s="2"/>
+      <c r="AU31" s="2"/>
+      <c r="AV31" s="2"/>
+      <c r="AW31" s="2"/>
+      <c r="AX31" s="2"/>
+      <c r="AY31" s="2"/>
+      <c r="AZ31" s="2"/>
+      <c r="BA31" s="2"/>
+      <c r="BB31" s="2"/>
+      <c r="BC31" s="2"/>
+      <c r="BD31" s="2"/>
+      <c r="BE31" s="2"/>
+      <c r="BF31" s="2"/>
+      <c r="BG31" s="2"/>
+      <c r="BH31" s="2"/>
+      <c r="BI31" s="2"/>
+      <c r="BJ31" s="2"/>
+      <c r="BK31" s="2"/>
+      <c r="BL31" s="2"/>
+      <c r="BM31" s="2"/>
+      <c r="BN31" s="2"/>
+      <c r="BO31" s="2"/>
+      <c r="BP31" s="2"/>
+      <c r="BQ31" s="2"/>
+      <c r="BR31" s="2"/>
+      <c r="BS31" s="2"/>
+      <c r="BT31" s="2"/>
+      <c r="BU31" s="2"/>
+      <c r="BV31" s="2"/>
+      <c r="BW31" s="2"/>
+      <c r="BX31" s="2"/>
+      <c r="BY31" s="2"/>
+      <c r="BZ31" s="2"/>
+      <c r="CA31" s="2"/>
+      <c r="CB31" s="2"/>
+      <c r="CC31" s="2"/>
+      <c r="CD31" s="2"/>
+      <c r="CE31" s="2"/>
+      <c r="CF31" s="2"/>
+      <c r="CG31" s="2"/>
+      <c r="CH31" s="2"/>
+      <c r="CI31" s="2"/>
+      <c r="CJ31" s="2"/>
+      <c r="CK31" s="2"/>
       <c r="CL31" s="2"/>
       <c r="CM31" s="2"/>
       <c r="CN31" s="2"/>
@@ -3453,92 +3749,92 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
-      <c r="AF32" s="1"/>
-      <c r="AG32" s="1"/>
-      <c r="AH32" s="1"/>
-      <c r="AI32" s="1"/>
-      <c r="AJ32" s="1"/>
-      <c r="AK32" s="5"/>
-      <c r="AL32" s="5"/>
-      <c r="AM32" s="5"/>
-      <c r="AN32" s="1"/>
-      <c r="AO32" s="1"/>
-      <c r="AP32" s="1"/>
-      <c r="AQ32" s="1"/>
-      <c r="AR32" s="1"/>
-      <c r="AS32" s="1"/>
-      <c r="AT32" s="1"/>
-      <c r="AU32" s="1"/>
-      <c r="AV32" s="1"/>
-      <c r="AW32" s="1"/>
-      <c r="AX32" s="1"/>
-      <c r="AY32" s="1"/>
-      <c r="AZ32" s="1"/>
-      <c r="BA32" s="5"/>
-      <c r="BB32" s="5"/>
-      <c r="BC32" s="5"/>
-      <c r="BD32" s="1"/>
-      <c r="BE32" s="1"/>
-      <c r="BF32" s="1"/>
-      <c r="BG32" s="1"/>
-      <c r="BH32" s="5"/>
-      <c r="BI32" s="1"/>
-      <c r="BJ32" s="1"/>
-      <c r="BK32" s="1"/>
-      <c r="BL32" s="5"/>
-      <c r="BM32" s="1"/>
-      <c r="BN32" s="1"/>
-      <c r="BO32" s="1"/>
-      <c r="BP32" s="1"/>
-      <c r="BQ32" s="5"/>
-      <c r="BR32" s="1"/>
-      <c r="BS32" s="1"/>
-      <c r="BT32" s="1"/>
-      <c r="BU32" s="5"/>
-      <c r="BV32" s="1"/>
-      <c r="BW32" s="1"/>
-      <c r="BX32" s="5"/>
-      <c r="BY32" s="1"/>
-      <c r="BZ32" s="5"/>
-      <c r="CA32" s="1"/>
-      <c r="CB32" s="1"/>
-      <c r="CC32" s="1"/>
-      <c r="CD32" s="5"/>
-      <c r="CE32" s="1"/>
-      <c r="CF32" s="1"/>
-      <c r="CG32" s="1"/>
-      <c r="CH32" s="5"/>
-      <c r="CI32" s="5"/>
-      <c r="CJ32" s="5"/>
-      <c r="CK32" s="4"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
+      <c r="AF32" s="2"/>
+      <c r="AG32" s="2"/>
+      <c r="AH32" s="2"/>
+      <c r="AI32" s="2"/>
+      <c r="AJ32" s="2"/>
+      <c r="AK32" s="2"/>
+      <c r="AL32" s="2"/>
+      <c r="AM32" s="2"/>
+      <c r="AN32" s="2"/>
+      <c r="AO32" s="2"/>
+      <c r="AP32" s="2"/>
+      <c r="AQ32" s="2"/>
+      <c r="AR32" s="2"/>
+      <c r="AS32" s="2"/>
+      <c r="AT32" s="2"/>
+      <c r="AU32" s="2"/>
+      <c r="AV32" s="2"/>
+      <c r="AW32" s="2"/>
+      <c r="AX32" s="2"/>
+      <c r="AY32" s="2"/>
+      <c r="AZ32" s="2"/>
+      <c r="BA32" s="2"/>
+      <c r="BB32" s="2"/>
+      <c r="BC32" s="2"/>
+      <c r="BD32" s="2"/>
+      <c r="BE32" s="2"/>
+      <c r="BF32" s="2"/>
+      <c r="BG32" s="2"/>
+      <c r="BH32" s="2"/>
+      <c r="BI32" s="2"/>
+      <c r="BJ32" s="2"/>
+      <c r="BK32" s="2"/>
+      <c r="BL32" s="2"/>
+      <c r="BM32" s="2"/>
+      <c r="BN32" s="2"/>
+      <c r="BO32" s="2"/>
+      <c r="BP32" s="2"/>
+      <c r="BQ32" s="2"/>
+      <c r="BR32" s="2"/>
+      <c r="BS32" s="2"/>
+      <c r="BT32" s="2"/>
+      <c r="BU32" s="2"/>
+      <c r="BV32" s="2"/>
+      <c r="BW32" s="2"/>
+      <c r="BX32" s="2"/>
+      <c r="BY32" s="2"/>
+      <c r="BZ32" s="2"/>
+      <c r="CA32" s="2"/>
+      <c r="CB32" s="2"/>
+      <c r="CC32" s="2"/>
+      <c r="CD32" s="2"/>
+      <c r="CE32" s="2"/>
+      <c r="CF32" s="2"/>
+      <c r="CG32" s="2"/>
+      <c r="CH32" s="2"/>
+      <c r="CI32" s="2"/>
+      <c r="CJ32" s="2"/>
+      <c r="CK32" s="2"/>
       <c r="CL32" s="2"/>
       <c r="CM32" s="2"/>
       <c r="CN32" s="2"/>
@@ -3548,92 +3844,92 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="1"/>
-      <c r="AC33" s="1"/>
-      <c r="AD33" s="1"/>
-      <c r="AE33" s="1"/>
-      <c r="AF33" s="1"/>
-      <c r="AG33" s="1"/>
-      <c r="AH33" s="1"/>
-      <c r="AI33" s="1"/>
-      <c r="AJ33" s="1"/>
-      <c r="AK33" s="5"/>
-      <c r="AL33" s="5"/>
-      <c r="AM33" s="5"/>
-      <c r="AN33" s="1"/>
-      <c r="AO33" s="1"/>
-      <c r="AP33" s="1"/>
-      <c r="AQ33" s="1"/>
-      <c r="AR33" s="1"/>
-      <c r="AS33" s="1"/>
-      <c r="AT33" s="1"/>
-      <c r="AU33" s="1"/>
-      <c r="AV33" s="1"/>
-      <c r="AW33" s="1"/>
-      <c r="AX33" s="1"/>
-      <c r="AY33" s="1"/>
-      <c r="AZ33" s="1"/>
-      <c r="BA33" s="5"/>
-      <c r="BB33" s="5"/>
-      <c r="BC33" s="5"/>
-      <c r="BD33" s="5"/>
-      <c r="BE33" s="5"/>
-      <c r="BF33" s="5"/>
-      <c r="BG33" s="5"/>
-      <c r="BH33" s="5"/>
-      <c r="BI33" s="5"/>
-      <c r="BJ33" s="5"/>
-      <c r="BK33" s="5"/>
-      <c r="BL33" s="5"/>
-      <c r="BM33" s="5"/>
-      <c r="BN33" s="5"/>
-      <c r="BO33" s="5"/>
-      <c r="BP33" s="5"/>
-      <c r="BQ33" s="5"/>
-      <c r="BR33" s="5"/>
-      <c r="BS33" s="5"/>
-      <c r="BT33" s="5"/>
-      <c r="BU33" s="5"/>
-      <c r="BV33" s="1"/>
-      <c r="BW33" s="1"/>
-      <c r="BX33" s="1"/>
-      <c r="BY33" s="5"/>
-      <c r="BZ33" s="5"/>
-      <c r="CA33" s="5"/>
-      <c r="CB33" s="5"/>
-      <c r="CC33" s="1"/>
-      <c r="CD33" s="5"/>
-      <c r="CE33" s="1"/>
-      <c r="CF33" s="1"/>
-      <c r="CG33" s="1"/>
-      <c r="CH33" s="5"/>
-      <c r="CI33" s="5"/>
-      <c r="CJ33" s="5"/>
-      <c r="CK33" s="4"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2"/>
+      <c r="AC33" s="2"/>
+      <c r="AD33" s="2"/>
+      <c r="AE33" s="2"/>
+      <c r="AF33" s="2"/>
+      <c r="AG33" s="2"/>
+      <c r="AH33" s="2"/>
+      <c r="AI33" s="2"/>
+      <c r="AJ33" s="2"/>
+      <c r="AK33" s="2"/>
+      <c r="AL33" s="2"/>
+      <c r="AM33" s="2"/>
+      <c r="AN33" s="2"/>
+      <c r="AO33" s="2"/>
+      <c r="AP33" s="2"/>
+      <c r="AQ33" s="2"/>
+      <c r="AR33" s="2"/>
+      <c r="AS33" s="2"/>
+      <c r="AT33" s="2"/>
+      <c r="AU33" s="2"/>
+      <c r="AV33" s="2"/>
+      <c r="AW33" s="2"/>
+      <c r="AX33" s="2"/>
+      <c r="AY33" s="2"/>
+      <c r="AZ33" s="2"/>
+      <c r="BA33" s="2"/>
+      <c r="BB33" s="2"/>
+      <c r="BC33" s="2"/>
+      <c r="BD33" s="2"/>
+      <c r="BE33" s="2"/>
+      <c r="BF33" s="2"/>
+      <c r="BG33" s="2"/>
+      <c r="BH33" s="2"/>
+      <c r="BI33" s="2"/>
+      <c r="BJ33" s="2"/>
+      <c r="BK33" s="2"/>
+      <c r="BL33" s="2"/>
+      <c r="BM33" s="2"/>
+      <c r="BN33" s="2"/>
+      <c r="BO33" s="2"/>
+      <c r="BP33" s="2"/>
+      <c r="BQ33" s="2"/>
+      <c r="BR33" s="2"/>
+      <c r="BS33" s="2"/>
+      <c r="BT33" s="2"/>
+      <c r="BU33" s="2"/>
+      <c r="BV33" s="2"/>
+      <c r="BW33" s="2"/>
+      <c r="BX33" s="2"/>
+      <c r="BY33" s="2"/>
+      <c r="BZ33" s="2"/>
+      <c r="CA33" s="2"/>
+      <c r="CB33" s="2"/>
+      <c r="CC33" s="2"/>
+      <c r="CD33" s="2"/>
+      <c r="CE33" s="2"/>
+      <c r="CF33" s="2"/>
+      <c r="CG33" s="2"/>
+      <c r="CH33" s="2"/>
+      <c r="CI33" s="2"/>
+      <c r="CJ33" s="2"/>
+      <c r="CK33" s="2"/>
       <c r="CL33" s="2"/>
       <c r="CM33" s="2"/>
       <c r="CN33" s="2"/>
@@ -3643,92 +3939,92 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
-      <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
-      <c r="AF34" s="1"/>
-      <c r="AG34" s="1"/>
-      <c r="AH34" s="1"/>
-      <c r="AI34" s="1"/>
-      <c r="AJ34" s="1"/>
-      <c r="AK34" s="5"/>
-      <c r="AL34" s="5"/>
-      <c r="AM34" s="5"/>
-      <c r="AN34" s="1"/>
-      <c r="AO34" s="1"/>
-      <c r="AP34" s="1"/>
-      <c r="AQ34" s="1"/>
-      <c r="AR34" s="1"/>
-      <c r="AS34" s="1"/>
-      <c r="AT34" s="1"/>
-      <c r="AU34" s="1"/>
-      <c r="AV34" s="1"/>
-      <c r="AW34" s="1"/>
-      <c r="AX34" s="1"/>
-      <c r="AY34" s="1"/>
-      <c r="AZ34" s="1"/>
-      <c r="BA34" s="5"/>
-      <c r="BB34" s="5"/>
-      <c r="BC34" s="5"/>
-      <c r="BD34" s="1"/>
-      <c r="BE34" s="1"/>
-      <c r="BF34" s="1"/>
-      <c r="BG34" s="1"/>
-      <c r="BH34" s="5"/>
-      <c r="BI34" s="1"/>
-      <c r="BJ34" s="1"/>
-      <c r="BK34" s="1"/>
-      <c r="BL34" s="5"/>
-      <c r="BM34" s="1"/>
-      <c r="BN34" s="1"/>
-      <c r="BO34" s="1"/>
-      <c r="BP34" s="1"/>
-      <c r="BQ34" s="5"/>
-      <c r="BR34" s="1"/>
-      <c r="BS34" s="1"/>
-      <c r="BT34" s="1"/>
-      <c r="BU34" s="5"/>
-      <c r="BV34" s="1"/>
-      <c r="BW34" s="1"/>
-      <c r="BX34" s="1"/>
-      <c r="BY34" s="1"/>
-      <c r="BZ34" s="5"/>
-      <c r="CA34" s="1"/>
-      <c r="CB34" s="1"/>
-      <c r="CC34" s="5"/>
-      <c r="CD34" s="5"/>
-      <c r="CE34" s="5"/>
-      <c r="CF34" s="1"/>
-      <c r="CG34" s="1"/>
-      <c r="CH34" s="5"/>
-      <c r="CI34" s="5"/>
-      <c r="CJ34" s="5"/>
-      <c r="CK34" s="4"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
+      <c r="AE34" s="2"/>
+      <c r="AF34" s="2"/>
+      <c r="AG34" s="2"/>
+      <c r="AH34" s="2"/>
+      <c r="AI34" s="2"/>
+      <c r="AJ34" s="2"/>
+      <c r="AK34" s="2"/>
+      <c r="AL34" s="2"/>
+      <c r="AM34" s="2"/>
+      <c r="AN34" s="2"/>
+      <c r="AO34" s="2"/>
+      <c r="AP34" s="2"/>
+      <c r="AQ34" s="2"/>
+      <c r="AR34" s="2"/>
+      <c r="AS34" s="2"/>
+      <c r="AT34" s="2"/>
+      <c r="AU34" s="2"/>
+      <c r="AV34" s="2"/>
+      <c r="AW34" s="2"/>
+      <c r="AX34" s="2"/>
+      <c r="AY34" s="2"/>
+      <c r="AZ34" s="2"/>
+      <c r="BA34" s="2"/>
+      <c r="BB34" s="2"/>
+      <c r="BC34" s="2"/>
+      <c r="BD34" s="2"/>
+      <c r="BE34" s="2"/>
+      <c r="BF34" s="2"/>
+      <c r="BG34" s="2"/>
+      <c r="BH34" s="2"/>
+      <c r="BI34" s="2"/>
+      <c r="BJ34" s="2"/>
+      <c r="BK34" s="2"/>
+      <c r="BL34" s="2"/>
+      <c r="BM34" s="2"/>
+      <c r="BN34" s="2"/>
+      <c r="BO34" s="2"/>
+      <c r="BP34" s="2"/>
+      <c r="BQ34" s="2"/>
+      <c r="BR34" s="2"/>
+      <c r="BS34" s="2"/>
+      <c r="BT34" s="2"/>
+      <c r="BU34" s="2"/>
+      <c r="BV34" s="2"/>
+      <c r="BW34" s="2"/>
+      <c r="BX34" s="2"/>
+      <c r="BY34" s="2"/>
+      <c r="BZ34" s="2"/>
+      <c r="CA34" s="2"/>
+      <c r="CB34" s="2"/>
+      <c r="CC34" s="2"/>
+      <c r="CD34" s="2"/>
+      <c r="CE34" s="2"/>
+      <c r="CF34" s="2"/>
+      <c r="CG34" s="2"/>
+      <c r="CH34" s="2"/>
+      <c r="CI34" s="2"/>
+      <c r="CJ34" s="2"/>
+      <c r="CK34" s="2"/>
       <c r="CL34" s="2"/>
       <c r="CM34" s="2"/>
       <c r="CN34" s="2"/>
@@ -3738,92 +4034,92 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
-      <c r="AF35" s="1"/>
-      <c r="AG35" s="1"/>
-      <c r="AH35" s="1"/>
-      <c r="AI35" s="1"/>
-      <c r="AJ35" s="1"/>
-      <c r="AK35" s="5"/>
-      <c r="AL35" s="5"/>
-      <c r="AM35" s="5"/>
-      <c r="AN35" s="1"/>
-      <c r="AO35" s="1"/>
-      <c r="AP35" s="1"/>
-      <c r="AQ35" s="1"/>
-      <c r="AR35" s="1"/>
-      <c r="AS35" s="1"/>
-      <c r="AT35" s="1"/>
-      <c r="AU35" s="1"/>
-      <c r="AV35" s="1"/>
-      <c r="AW35" s="1"/>
-      <c r="AX35" s="1"/>
-      <c r="AY35" s="1"/>
-      <c r="AZ35" s="1"/>
-      <c r="BA35" s="5"/>
-      <c r="BB35" s="5"/>
-      <c r="BC35" s="5"/>
-      <c r="BD35" s="1"/>
-      <c r="BE35" s="1"/>
-      <c r="BF35" s="1"/>
-      <c r="BG35" s="1"/>
-      <c r="BH35" s="5"/>
-      <c r="BI35" s="1"/>
-      <c r="BJ35" s="1"/>
-      <c r="BK35" s="1"/>
-      <c r="BL35" s="5"/>
-      <c r="BM35" s="1"/>
-      <c r="BN35" s="1"/>
-      <c r="BO35" s="1"/>
-      <c r="BP35" s="1"/>
-      <c r="BQ35" s="5"/>
-      <c r="BR35" s="1"/>
-      <c r="BS35" s="1"/>
-      <c r="BT35" s="1"/>
-      <c r="BU35" s="5"/>
-      <c r="BV35" s="1"/>
-      <c r="BW35" s="1"/>
-      <c r="BX35" s="1"/>
-      <c r="BY35" s="1"/>
-      <c r="BZ35" s="5"/>
-      <c r="CA35" s="1"/>
-      <c r="CB35" s="1"/>
-      <c r="CC35" s="1"/>
-      <c r="CD35" s="5"/>
-      <c r="CE35" s="1"/>
-      <c r="CF35" s="5"/>
-      <c r="CG35" s="5"/>
-      <c r="CH35" s="5"/>
-      <c r="CI35" s="5"/>
-      <c r="CJ35" s="5"/>
-      <c r="CK35" s="4"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="2"/>
+      <c r="AE35" s="2"/>
+      <c r="AF35" s="2"/>
+      <c r="AG35" s="2"/>
+      <c r="AH35" s="2"/>
+      <c r="AI35" s="2"/>
+      <c r="AJ35" s="2"/>
+      <c r="AK35" s="2"/>
+      <c r="AL35" s="2"/>
+      <c r="AM35" s="2"/>
+      <c r="AN35" s="2"/>
+      <c r="AO35" s="2"/>
+      <c r="AP35" s="2"/>
+      <c r="AQ35" s="2"/>
+      <c r="AR35" s="2"/>
+      <c r="AS35" s="2"/>
+      <c r="AT35" s="2"/>
+      <c r="AU35" s="2"/>
+      <c r="AV35" s="2"/>
+      <c r="AW35" s="2"/>
+      <c r="AX35" s="2"/>
+      <c r="AY35" s="2"/>
+      <c r="AZ35" s="2"/>
+      <c r="BA35" s="2"/>
+      <c r="BB35" s="2"/>
+      <c r="BC35" s="2"/>
+      <c r="BD35" s="2"/>
+      <c r="BE35" s="2"/>
+      <c r="BF35" s="2"/>
+      <c r="BG35" s="2"/>
+      <c r="BH35" s="2"/>
+      <c r="BI35" s="2"/>
+      <c r="BJ35" s="2"/>
+      <c r="BK35" s="2"/>
+      <c r="BL35" s="2"/>
+      <c r="BM35" s="2"/>
+      <c r="BN35" s="2"/>
+      <c r="BO35" s="2"/>
+      <c r="BP35" s="2"/>
+      <c r="BQ35" s="2"/>
+      <c r="BR35" s="2"/>
+      <c r="BS35" s="2"/>
+      <c r="BT35" s="2"/>
+      <c r="BU35" s="2"/>
+      <c r="BV35" s="2"/>
+      <c r="BW35" s="2"/>
+      <c r="BX35" s="2"/>
+      <c r="BY35" s="2"/>
+      <c r="BZ35" s="2"/>
+      <c r="CA35" s="2"/>
+      <c r="CB35" s="2"/>
+      <c r="CC35" s="2"/>
+      <c r="CD35" s="2"/>
+      <c r="CE35" s="2"/>
+      <c r="CF35" s="2"/>
+      <c r="CG35" s="2"/>
+      <c r="CH35" s="2"/>
+      <c r="CI35" s="2"/>
+      <c r="CJ35" s="2"/>
+      <c r="CK35" s="2"/>
       <c r="CL35" s="2"/>
       <c r="CM35" s="2"/>
       <c r="CN35" s="2"/>
@@ -3833,92 +4129,92 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
-      <c r="AF36" s="1"/>
-      <c r="AG36" s="1"/>
-      <c r="AH36" s="1"/>
-      <c r="AI36" s="1"/>
-      <c r="AJ36" s="1"/>
-      <c r="AK36" s="5"/>
-      <c r="AL36" s="5"/>
-      <c r="AM36" s="5"/>
-      <c r="AN36" s="1"/>
-      <c r="AO36" s="1"/>
-      <c r="AP36" s="1"/>
-      <c r="AQ36" s="1"/>
-      <c r="AR36" s="1"/>
-      <c r="AS36" s="1"/>
-      <c r="AT36" s="1"/>
-      <c r="AU36" s="1"/>
-      <c r="AV36" s="1"/>
-      <c r="AW36" s="1"/>
-      <c r="AX36" s="1"/>
-      <c r="AY36" s="1"/>
-      <c r="AZ36" s="1"/>
-      <c r="BA36" s="5"/>
-      <c r="BB36" s="5"/>
-      <c r="BC36" s="5"/>
-      <c r="BD36" s="5"/>
-      <c r="BE36" s="5"/>
-      <c r="BF36" s="5"/>
-      <c r="BG36" s="5"/>
-      <c r="BH36" s="5"/>
-      <c r="BI36" s="5"/>
-      <c r="BJ36" s="5"/>
-      <c r="BK36" s="5"/>
-      <c r="BL36" s="5"/>
-      <c r="BM36" s="5"/>
-      <c r="BN36" s="5"/>
-      <c r="BO36" s="5"/>
-      <c r="BP36" s="5"/>
-      <c r="BQ36" s="5"/>
-      <c r="BR36" s="5"/>
-      <c r="BS36" s="5"/>
-      <c r="BT36" s="5"/>
-      <c r="BU36" s="5"/>
-      <c r="BV36" s="5"/>
-      <c r="BW36" s="5"/>
-      <c r="BX36" s="5"/>
-      <c r="BY36" s="5"/>
-      <c r="BZ36" s="5"/>
-      <c r="CA36" s="1"/>
-      <c r="CB36" s="1"/>
-      <c r="CC36" s="1"/>
-      <c r="CD36" s="5"/>
-      <c r="CE36" s="1"/>
-      <c r="CF36" s="1"/>
-      <c r="CG36" s="1"/>
-      <c r="CH36" s="5"/>
-      <c r="CI36" s="5"/>
-      <c r="CJ36" s="5"/>
-      <c r="CK36" s="4"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="2"/>
+      <c r="AE36" s="2"/>
+      <c r="AF36" s="2"/>
+      <c r="AG36" s="2"/>
+      <c r="AH36" s="2"/>
+      <c r="AI36" s="2"/>
+      <c r="AJ36" s="2"/>
+      <c r="AK36" s="2"/>
+      <c r="AL36" s="2"/>
+      <c r="AM36" s="2"/>
+      <c r="AN36" s="2"/>
+      <c r="AO36" s="2"/>
+      <c r="AP36" s="2"/>
+      <c r="AQ36" s="2"/>
+      <c r="AR36" s="2"/>
+      <c r="AS36" s="2"/>
+      <c r="AT36" s="2"/>
+      <c r="AU36" s="2"/>
+      <c r="AV36" s="2"/>
+      <c r="AW36" s="2"/>
+      <c r="AX36" s="2"/>
+      <c r="AY36" s="2"/>
+      <c r="AZ36" s="2"/>
+      <c r="BA36" s="2"/>
+      <c r="BB36" s="2"/>
+      <c r="BC36" s="2"/>
+      <c r="BD36" s="2"/>
+      <c r="BE36" s="2"/>
+      <c r="BF36" s="2"/>
+      <c r="BG36" s="2"/>
+      <c r="BH36" s="2"/>
+      <c r="BI36" s="2"/>
+      <c r="BJ36" s="2"/>
+      <c r="BK36" s="2"/>
+      <c r="BL36" s="2"/>
+      <c r="BM36" s="2"/>
+      <c r="BN36" s="2"/>
+      <c r="BO36" s="2"/>
+      <c r="BP36" s="2"/>
+      <c r="BQ36" s="2"/>
+      <c r="BR36" s="2"/>
+      <c r="BS36" s="2"/>
+      <c r="BT36" s="2"/>
+      <c r="BU36" s="2"/>
+      <c r="BV36" s="2"/>
+      <c r="BW36" s="2"/>
+      <c r="BX36" s="2"/>
+      <c r="BY36" s="2"/>
+      <c r="BZ36" s="2"/>
+      <c r="CA36" s="2"/>
+      <c r="CB36" s="2"/>
+      <c r="CC36" s="2"/>
+      <c r="CD36" s="2"/>
+      <c r="CE36" s="2"/>
+      <c r="CF36" s="2"/>
+      <c r="CG36" s="2"/>
+      <c r="CH36" s="2"/>
+      <c r="CI36" s="2"/>
+      <c r="CJ36" s="2"/>
+      <c r="CK36" s="2"/>
       <c r="CL36" s="2"/>
       <c r="CM36" s="2"/>
       <c r="CN36" s="2"/>
@@ -3928,92 +4224,92 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
-      <c r="AF37" s="1"/>
-      <c r="AG37" s="1"/>
-      <c r="AH37" s="1"/>
-      <c r="AI37" s="1"/>
-      <c r="AJ37" s="1"/>
-      <c r="AK37" s="5"/>
-      <c r="AL37" s="5"/>
-      <c r="AM37" s="5"/>
-      <c r="AN37" s="1"/>
-      <c r="AO37" s="1"/>
-      <c r="AP37" s="1"/>
-      <c r="AQ37" s="1"/>
-      <c r="AR37" s="1"/>
-      <c r="AS37" s="1"/>
-      <c r="AT37" s="1"/>
-      <c r="AU37" s="1"/>
-      <c r="AV37" s="1"/>
-      <c r="AW37" s="1"/>
-      <c r="AX37" s="1"/>
-      <c r="AY37" s="1"/>
-      <c r="AZ37" s="1"/>
-      <c r="BA37" s="5"/>
-      <c r="BB37" s="5"/>
-      <c r="BC37" s="5"/>
-      <c r="BD37" s="1"/>
-      <c r="BE37" s="1"/>
-      <c r="BF37" s="1"/>
-      <c r="BG37" s="1"/>
-      <c r="BH37" s="5"/>
-      <c r="BI37" s="1"/>
-      <c r="BJ37" s="1"/>
-      <c r="BK37" s="1"/>
-      <c r="BL37" s="5"/>
-      <c r="BM37" s="1"/>
-      <c r="BN37" s="1"/>
-      <c r="BO37" s="1"/>
-      <c r="BP37" s="1"/>
-      <c r="BQ37" s="5"/>
-      <c r="BR37" s="1"/>
-      <c r="BS37" s="1"/>
-      <c r="BT37" s="1"/>
-      <c r="BU37" s="5"/>
-      <c r="BV37" s="1"/>
-      <c r="BW37" s="1"/>
-      <c r="BX37" s="1"/>
-      <c r="BY37" s="1"/>
-      <c r="BZ37" s="5"/>
-      <c r="CA37" s="1"/>
-      <c r="CB37" s="1"/>
-      <c r="CC37" s="1"/>
-      <c r="CD37" s="5"/>
-      <c r="CE37" s="1"/>
-      <c r="CF37" s="1"/>
-      <c r="CG37" s="1"/>
-      <c r="CH37" s="5"/>
-      <c r="CI37" s="5"/>
-      <c r="CJ37" s="5"/>
-      <c r="CK37" s="4"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="2"/>
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="2"/>
+      <c r="AE37" s="2"/>
+      <c r="AF37" s="2"/>
+      <c r="AG37" s="2"/>
+      <c r="AH37" s="2"/>
+      <c r="AI37" s="2"/>
+      <c r="AJ37" s="2"/>
+      <c r="AK37" s="2"/>
+      <c r="AL37" s="2"/>
+      <c r="AM37" s="2"/>
+      <c r="AN37" s="2"/>
+      <c r="AO37" s="2"/>
+      <c r="AP37" s="2"/>
+      <c r="AQ37" s="2"/>
+      <c r="AR37" s="2"/>
+      <c r="AS37" s="2"/>
+      <c r="AT37" s="2"/>
+      <c r="AU37" s="2"/>
+      <c r="AV37" s="2"/>
+      <c r="AW37" s="2"/>
+      <c r="AX37" s="2"/>
+      <c r="AY37" s="2"/>
+      <c r="AZ37" s="2"/>
+      <c r="BA37" s="2"/>
+      <c r="BB37" s="2"/>
+      <c r="BC37" s="2"/>
+      <c r="BD37" s="2"/>
+      <c r="BE37" s="2"/>
+      <c r="BF37" s="2"/>
+      <c r="BG37" s="2"/>
+      <c r="BH37" s="2"/>
+      <c r="BI37" s="2"/>
+      <c r="BJ37" s="2"/>
+      <c r="BK37" s="2"/>
+      <c r="BL37" s="2"/>
+      <c r="BM37" s="2"/>
+      <c r="BN37" s="2"/>
+      <c r="BO37" s="2"/>
+      <c r="BP37" s="2"/>
+      <c r="BQ37" s="2"/>
+      <c r="BR37" s="2"/>
+      <c r="BS37" s="2"/>
+      <c r="BT37" s="2"/>
+      <c r="BU37" s="2"/>
+      <c r="BV37" s="2"/>
+      <c r="BW37" s="2"/>
+      <c r="BX37" s="2"/>
+      <c r="BY37" s="2"/>
+      <c r="BZ37" s="2"/>
+      <c r="CA37" s="2"/>
+      <c r="CB37" s="2"/>
+      <c r="CC37" s="2"/>
+      <c r="CD37" s="2"/>
+      <c r="CE37" s="2"/>
+      <c r="CF37" s="2"/>
+      <c r="CG37" s="2"/>
+      <c r="CH37" s="2"/>
+      <c r="CI37" s="2"/>
+      <c r="CJ37" s="2"/>
+      <c r="CK37" s="2"/>
       <c r="CL37" s="2"/>
       <c r="CM37" s="2"/>
       <c r="CN37" s="2"/>
@@ -4023,92 +4319,92 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
-      <c r="AF38" s="1"/>
-      <c r="AG38" s="1"/>
-      <c r="AH38" s="1"/>
-      <c r="AI38" s="1"/>
-      <c r="AJ38" s="1"/>
-      <c r="AK38" s="5"/>
-      <c r="AL38" s="5"/>
-      <c r="AM38" s="5"/>
-      <c r="AN38" s="1"/>
-      <c r="AO38" s="1"/>
-      <c r="AP38" s="1"/>
-      <c r="AQ38" s="1"/>
-      <c r="AR38" s="1"/>
-      <c r="AS38" s="1"/>
-      <c r="AT38" s="1"/>
-      <c r="AU38" s="1"/>
-      <c r="AV38" s="1"/>
-      <c r="AW38" s="1"/>
-      <c r="AX38" s="1"/>
-      <c r="AY38" s="1"/>
-      <c r="AZ38" s="1"/>
-      <c r="BA38" s="5"/>
-      <c r="BB38" s="5"/>
-      <c r="BC38" s="5"/>
-      <c r="BD38" s="1"/>
-      <c r="BE38" s="1"/>
-      <c r="BF38" s="1"/>
-      <c r="BG38" s="1"/>
-      <c r="BH38" s="5"/>
-      <c r="BI38" s="1"/>
-      <c r="BJ38" s="1"/>
-      <c r="BK38" s="1"/>
-      <c r="BL38" s="5"/>
-      <c r="BM38" s="1"/>
-      <c r="BN38" s="1"/>
-      <c r="BO38" s="1"/>
-      <c r="BP38" s="1"/>
-      <c r="BQ38" s="5"/>
-      <c r="BR38" s="1"/>
-      <c r="BS38" s="1"/>
-      <c r="BT38" s="1"/>
-      <c r="BU38" s="5"/>
-      <c r="BV38" s="1"/>
-      <c r="BW38" s="1"/>
-      <c r="BX38" s="1"/>
-      <c r="BY38" s="1"/>
-      <c r="BZ38" s="5"/>
-      <c r="CA38" s="1"/>
-      <c r="CB38" s="1"/>
-      <c r="CC38" s="1"/>
-      <c r="CD38" s="5"/>
-      <c r="CE38" s="1"/>
-      <c r="CF38" s="1"/>
-      <c r="CG38" s="1"/>
-      <c r="CH38" s="5"/>
-      <c r="CI38" s="5"/>
-      <c r="CJ38" s="5"/>
-      <c r="CK38" s="4"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2"/>
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="2"/>
+      <c r="AE38" s="2"/>
+      <c r="AF38" s="2"/>
+      <c r="AG38" s="2"/>
+      <c r="AH38" s="2"/>
+      <c r="AI38" s="2"/>
+      <c r="AJ38" s="2"/>
+      <c r="AK38" s="2"/>
+      <c r="AL38" s="2"/>
+      <c r="AM38" s="2"/>
+      <c r="AN38" s="2"/>
+      <c r="AO38" s="2"/>
+      <c r="AP38" s="2"/>
+      <c r="AQ38" s="2"/>
+      <c r="AR38" s="2"/>
+      <c r="AS38" s="2"/>
+      <c r="AT38" s="2"/>
+      <c r="AU38" s="2"/>
+      <c r="AV38" s="2"/>
+      <c r="AW38" s="2"/>
+      <c r="AX38" s="2"/>
+      <c r="AY38" s="2"/>
+      <c r="AZ38" s="2"/>
+      <c r="BA38" s="2"/>
+      <c r="BB38" s="2"/>
+      <c r="BC38" s="2"/>
+      <c r="BD38" s="2"/>
+      <c r="BE38" s="2"/>
+      <c r="BF38" s="2"/>
+      <c r="BG38" s="2"/>
+      <c r="BH38" s="2"/>
+      <c r="BI38" s="2"/>
+      <c r="BJ38" s="2"/>
+      <c r="BK38" s="2"/>
+      <c r="BL38" s="2"/>
+      <c r="BM38" s="2"/>
+      <c r="BN38" s="2"/>
+      <c r="BO38" s="2"/>
+      <c r="BP38" s="2"/>
+      <c r="BQ38" s="2"/>
+      <c r="BR38" s="2"/>
+      <c r="BS38" s="2"/>
+      <c r="BT38" s="2"/>
+      <c r="BU38" s="2"/>
+      <c r="BV38" s="2"/>
+      <c r="BW38" s="2"/>
+      <c r="BX38" s="2"/>
+      <c r="BY38" s="2"/>
+      <c r="BZ38" s="2"/>
+      <c r="CA38" s="2"/>
+      <c r="CB38" s="2"/>
+      <c r="CC38" s="2"/>
+      <c r="CD38" s="2"/>
+      <c r="CE38" s="2"/>
+      <c r="CF38" s="2"/>
+      <c r="CG38" s="2"/>
+      <c r="CH38" s="2"/>
+      <c r="CI38" s="2"/>
+      <c r="CJ38" s="2"/>
+      <c r="CK38" s="2"/>
       <c r="CL38" s="2"/>
       <c r="CM38" s="2"/>
       <c r="CN38" s="2"/>
@@ -4118,92 +4414,92 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
-      <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
-      <c r="AF39" s="1"/>
-      <c r="AG39" s="1"/>
-      <c r="AH39" s="1"/>
-      <c r="AI39" s="1"/>
-      <c r="AJ39" s="1"/>
-      <c r="AK39" s="5"/>
-      <c r="AL39" s="5"/>
-      <c r="AM39" s="5"/>
-      <c r="AN39" s="1"/>
-      <c r="AO39" s="1"/>
-      <c r="AP39" s="1"/>
-      <c r="AQ39" s="1"/>
-      <c r="AR39" s="1"/>
-      <c r="AS39" s="1"/>
-      <c r="AT39" s="1"/>
-      <c r="AU39" s="1"/>
-      <c r="AV39" s="1"/>
-      <c r="AW39" s="1"/>
-      <c r="AX39" s="1"/>
-      <c r="AY39" s="1"/>
-      <c r="AZ39" s="1"/>
-      <c r="BA39" s="5"/>
-      <c r="BB39" s="5"/>
-      <c r="BC39" s="5"/>
-      <c r="BD39" s="1"/>
-      <c r="BE39" s="1"/>
-      <c r="BF39" s="1"/>
-      <c r="BG39" s="1"/>
-      <c r="BH39" s="5"/>
-      <c r="BI39" s="1"/>
-      <c r="BJ39" s="1"/>
-      <c r="BK39" s="1"/>
-      <c r="BL39" s="5"/>
-      <c r="BM39" s="1"/>
-      <c r="BN39" s="1"/>
-      <c r="BO39" s="1"/>
-      <c r="BP39" s="1"/>
-      <c r="BQ39" s="5"/>
-      <c r="BR39" s="1"/>
-      <c r="BS39" s="1"/>
-      <c r="BT39" s="1"/>
-      <c r="BU39" s="5"/>
-      <c r="BV39" s="1"/>
-      <c r="BW39" s="1"/>
-      <c r="BX39" s="1"/>
-      <c r="BY39" s="1"/>
-      <c r="BZ39" s="5"/>
-      <c r="CA39" s="1"/>
-      <c r="CB39" s="1"/>
-      <c r="CC39" s="1"/>
-      <c r="CD39" s="5"/>
-      <c r="CE39" s="1"/>
-      <c r="CF39" s="1"/>
-      <c r="CG39" s="1"/>
-      <c r="CH39" s="5"/>
-      <c r="CI39" s="5"/>
-      <c r="CJ39" s="5"/>
-      <c r="CK39" s="4"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+      <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
+      <c r="AA39" s="2"/>
+      <c r="AB39" s="2"/>
+      <c r="AC39" s="2"/>
+      <c r="AD39" s="2"/>
+      <c r="AE39" s="2"/>
+      <c r="AF39" s="2"/>
+      <c r="AG39" s="2"/>
+      <c r="AH39" s="2"/>
+      <c r="AI39" s="2"/>
+      <c r="AJ39" s="2"/>
+      <c r="AK39" s="2"/>
+      <c r="AL39" s="2"/>
+      <c r="AM39" s="2"/>
+      <c r="AN39" s="2"/>
+      <c r="AO39" s="2"/>
+      <c r="AP39" s="2"/>
+      <c r="AQ39" s="2"/>
+      <c r="AR39" s="2"/>
+      <c r="AS39" s="2"/>
+      <c r="AT39" s="2"/>
+      <c r="AU39" s="2"/>
+      <c r="AV39" s="2"/>
+      <c r="AW39" s="2"/>
+      <c r="AX39" s="2"/>
+      <c r="AY39" s="2"/>
+      <c r="AZ39" s="2"/>
+      <c r="BA39" s="2"/>
+      <c r="BB39" s="2"/>
+      <c r="BC39" s="2"/>
+      <c r="BD39" s="2"/>
+      <c r="BE39" s="2"/>
+      <c r="BF39" s="2"/>
+      <c r="BG39" s="2"/>
+      <c r="BH39" s="2"/>
+      <c r="BI39" s="2"/>
+      <c r="BJ39" s="2"/>
+      <c r="BK39" s="2"/>
+      <c r="BL39" s="2"/>
+      <c r="BM39" s="2"/>
+      <c r="BN39" s="2"/>
+      <c r="BO39" s="2"/>
+      <c r="BP39" s="2"/>
+      <c r="BQ39" s="2"/>
+      <c r="BR39" s="2"/>
+      <c r="BS39" s="2"/>
+      <c r="BT39" s="2"/>
+      <c r="BU39" s="2"/>
+      <c r="BV39" s="2"/>
+      <c r="BW39" s="2"/>
+      <c r="BX39" s="2"/>
+      <c r="BY39" s="2"/>
+      <c r="BZ39" s="2"/>
+      <c r="CA39" s="2"/>
+      <c r="CB39" s="2"/>
+      <c r="CC39" s="2"/>
+      <c r="CD39" s="2"/>
+      <c r="CE39" s="2"/>
+      <c r="CF39" s="2"/>
+      <c r="CG39" s="2"/>
+      <c r="CH39" s="2"/>
+      <c r="CI39" s="2"/>
+      <c r="CJ39" s="2"/>
+      <c r="CK39" s="2"/>
       <c r="CL39" s="2"/>
       <c r="CM39" s="2"/>
       <c r="CN39" s="2"/>
@@ -4399,7 +4695,7 @@
       <c r="CN41" s="2"/>
       <c r="CO41" s="2"/>
     </row>
-    <row r="42" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4432,10 +4728,10 @@
       <c r="AD42" s="5"/>
       <c r="AE42" s="5"/>
       <c r="AF42" s="5"/>
-      <c r="AG42" s="5"/>
-      <c r="AH42" s="5"/>
-      <c r="AI42" s="5"/>
-      <c r="AJ42" s="5"/>
+      <c r="AG42" s="11"/>
+      <c r="AH42" s="11"/>
+      <c r="AI42" s="11"/>
+      <c r="AJ42" s="11"/>
       <c r="AK42" s="5"/>
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
@@ -4526,12 +4822,12 @@
       <c r="AC43" s="1"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="6"/>
-      <c r="AF43" s="5"/>
-      <c r="AG43" s="1"/>
-      <c r="AH43" s="1"/>
-      <c r="AI43" s="1"/>
-      <c r="AJ43" s="1"/>
-      <c r="AK43" s="5"/>
+      <c r="AF43" s="9"/>
+      <c r="AG43" s="15"/>
+      <c r="AH43" s="16"/>
+      <c r="AI43" s="16"/>
+      <c r="AJ43" s="17"/>
+      <c r="AK43" s="10"/>
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
       <c r="AN43" s="6"/>
@@ -4621,12 +4917,12 @@
       <c r="AC44" s="1"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="6"/>
-      <c r="AF44" s="5"/>
-      <c r="AG44" s="1"/>
+      <c r="AF44" s="9"/>
+      <c r="AG44" s="18"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
-      <c r="AJ44" s="1"/>
-      <c r="AK44" s="5"/>
+      <c r="AJ44" s="19"/>
+      <c r="AK44" s="10"/>
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
       <c r="AN44" s="6"/>
@@ -4684,7 +4980,7 @@
       <c r="CN44" s="2"/>
       <c r="CO44" s="2"/>
     </row>
-    <row r="45" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4716,12 +5012,12 @@
       <c r="AC45" s="1"/>
       <c r="AD45" s="5"/>
       <c r="AE45" s="6"/>
-      <c r="AF45" s="5"/>
-      <c r="AG45" s="1"/>
-      <c r="AH45" s="1"/>
-      <c r="AI45" s="1"/>
-      <c r="AJ45" s="1"/>
-      <c r="AK45" s="5"/>
+      <c r="AF45" s="9"/>
+      <c r="AG45" s="20"/>
+      <c r="AH45" s="21"/>
+      <c r="AI45" s="21"/>
+      <c r="AJ45" s="22"/>
+      <c r="AK45" s="10"/>
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
       <c r="AN45" s="6"/>
@@ -4779,7 +5075,7 @@
       <c r="CN45" s="2"/>
       <c r="CO45" s="2"/>
     </row>
-    <row r="46" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4812,10 +5108,10 @@
       <c r="AD46" s="5"/>
       <c r="AE46" s="5"/>
       <c r="AF46" s="5"/>
-      <c r="AG46" s="5"/>
-      <c r="AH46" s="5"/>
-      <c r="AI46" s="5"/>
-      <c r="AJ46" s="5"/>
+      <c r="AG46" s="23"/>
+      <c r="AH46" s="23"/>
+      <c r="AI46" s="23"/>
+      <c r="AJ46" s="23"/>
       <c r="AK46" s="5"/>
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
@@ -4906,12 +5202,12 @@
       <c r="AC47" s="1"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="6"/>
-      <c r="AF47" s="5"/>
-      <c r="AG47" s="1"/>
-      <c r="AH47" s="1"/>
-      <c r="AI47" s="1"/>
-      <c r="AJ47" s="1"/>
-      <c r="AK47" s="5"/>
+      <c r="AF47" s="9"/>
+      <c r="AG47" s="15"/>
+      <c r="AH47" s="17"/>
+      <c r="AI47" s="15"/>
+      <c r="AJ47" s="17"/>
+      <c r="AK47" s="10"/>
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
       <c r="AN47" s="6"/>
@@ -4969,7 +5265,7 @@
       <c r="CN47" s="2"/>
       <c r="CO47" s="2"/>
     </row>
-    <row r="48" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -5001,12 +5297,12 @@
       <c r="AC48" s="1"/>
       <c r="AD48" s="5"/>
       <c r="AE48" s="6"/>
-      <c r="AF48" s="5"/>
-      <c r="AG48" s="1"/>
-      <c r="AH48" s="1"/>
-      <c r="AI48" s="1"/>
-      <c r="AJ48" s="1"/>
-      <c r="AK48" s="5"/>
+      <c r="AF48" s="9"/>
+      <c r="AG48" s="18"/>
+      <c r="AH48" s="19"/>
+      <c r="AI48" s="20"/>
+      <c r="AJ48" s="22"/>
+      <c r="AK48" s="10"/>
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
       <c r="AN48" s="6"/>
@@ -5064,7 +5360,7 @@
       <c r="CN48" s="2"/>
       <c r="CO48" s="2"/>
     </row>
-    <row r="49" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -5096,11 +5392,11 @@
       <c r="AC49" s="1"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="6"/>
-      <c r="AF49" s="5"/>
-      <c r="AG49" s="1"/>
-      <c r="AH49" s="1"/>
-      <c r="AI49" s="1"/>
-      <c r="AJ49" s="1"/>
+      <c r="AF49" s="9"/>
+      <c r="AG49" s="20"/>
+      <c r="AH49" s="22"/>
+      <c r="AI49" s="13"/>
+      <c r="AJ49" s="12"/>
       <c r="AK49" s="5"/>
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
@@ -5159,7 +5455,7 @@
       <c r="CN49" s="2"/>
       <c r="CO49" s="2"/>
     </row>
-    <row r="50" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5186,16 +5482,16 @@
       <c r="X50" s="5"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
-      <c r="AA50" s="5"/>
-      <c r="AB50" s="5"/>
-      <c r="AC50" s="5"/>
+      <c r="AA50" s="11"/>
+      <c r="AB50" s="11"/>
+      <c r="AC50" s="11"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5"/>
       <c r="AF50" s="5"/>
-      <c r="AG50" s="5"/>
-      <c r="AH50" s="5"/>
-      <c r="AI50" s="5"/>
-      <c r="AJ50" s="5"/>
+      <c r="AG50" s="23"/>
+      <c r="AH50" s="23"/>
+      <c r="AI50" s="11"/>
+      <c r="AJ50" s="11"/>
       <c r="AK50" s="5"/>
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
@@ -5280,18 +5576,18 @@
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
-      <c r="Z51" s="5"/>
-      <c r="AA51" s="1"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="1"/>
-      <c r="AD51" s="5"/>
+      <c r="Z51" s="9"/>
+      <c r="AA51" s="25"/>
+      <c r="AB51" s="15"/>
+      <c r="AC51" s="17"/>
+      <c r="AD51" s="10"/>
       <c r="AE51" s="6"/>
-      <c r="AF51" s="5"/>
-      <c r="AG51" s="1"/>
-      <c r="AH51" s="1"/>
-      <c r="AI51" s="1"/>
-      <c r="AJ51" s="1"/>
-      <c r="AK51" s="5"/>
+      <c r="AF51" s="9"/>
+      <c r="AG51" s="15"/>
+      <c r="AH51" s="16"/>
+      <c r="AI51" s="16"/>
+      <c r="AJ51" s="17"/>
+      <c r="AK51" s="10"/>
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
       <c r="AN51" s="6"/>
@@ -5349,7 +5645,7 @@
       <c r="CN51" s="2"/>
       <c r="CO51" s="2"/>
     </row>
-    <row r="52" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5375,18 +5671,18 @@
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
-      <c r="Z52" s="5"/>
-      <c r="AA52" s="1"/>
-      <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
-      <c r="AD52" s="5"/>
+      <c r="Z52" s="9"/>
+      <c r="AA52" s="26"/>
+      <c r="AB52" s="20"/>
+      <c r="AC52" s="22"/>
+      <c r="AD52" s="10"/>
       <c r="AE52" s="6"/>
-      <c r="AF52" s="5"/>
-      <c r="AG52" s="1"/>
-      <c r="AH52" s="1"/>
-      <c r="AI52" s="1"/>
-      <c r="AJ52" s="1"/>
-      <c r="AK52" s="5"/>
+      <c r="AF52" s="9"/>
+      <c r="AG52" s="20"/>
+      <c r="AH52" s="21"/>
+      <c r="AI52" s="21"/>
+      <c r="AJ52" s="22"/>
+      <c r="AK52" s="10"/>
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
       <c r="AN52" s="6"/>
@@ -5444,7 +5740,7 @@
       <c r="CN52" s="2"/>
       <c r="CO52" s="2"/>
     </row>
-    <row r="53" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5470,17 +5766,17 @@
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="Z53" s="5"/>
-      <c r="AA53" s="1"/>
-      <c r="AB53" s="1"/>
-      <c r="AC53" s="1"/>
-      <c r="AD53" s="5"/>
+      <c r="Z53" s="9"/>
+      <c r="AA53" s="27"/>
+      <c r="AB53" s="15"/>
+      <c r="AC53" s="17"/>
+      <c r="AD53" s="10"/>
       <c r="AE53" s="6"/>
       <c r="AF53" s="5"/>
-      <c r="AG53" s="1"/>
-      <c r="AH53" s="1"/>
-      <c r="AI53" s="1"/>
-      <c r="AJ53" s="1"/>
+      <c r="AG53" s="24"/>
+      <c r="AH53" s="24"/>
+      <c r="AI53" s="24"/>
+      <c r="AJ53" s="24"/>
       <c r="AK53" s="5"/>
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
@@ -5539,7 +5835,7 @@
       <c r="CN53" s="2"/>
       <c r="CO53" s="2"/>
     </row>
-    <row r="54" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5565,18 +5861,18 @@
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
-      <c r="Z54" s="5"/>
-      <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
-      <c r="AD54" s="5"/>
+      <c r="Z54" s="9"/>
+      <c r="AA54" s="25"/>
+      <c r="AB54" s="20"/>
+      <c r="AC54" s="22"/>
+      <c r="AD54" s="10"/>
       <c r="AE54" s="6"/>
-      <c r="AF54" s="5"/>
-      <c r="AG54" s="1"/>
-      <c r="AH54" s="1"/>
-      <c r="AI54" s="1"/>
-      <c r="AJ54" s="1"/>
-      <c r="AK54" s="5"/>
+      <c r="AF54" s="9"/>
+      <c r="AG54" s="15"/>
+      <c r="AH54" s="16"/>
+      <c r="AI54" s="16"/>
+      <c r="AJ54" s="17"/>
+      <c r="AK54" s="10"/>
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
       <c r="AN54" s="6"/>
@@ -5660,18 +5956,18 @@
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
-      <c r="Z55" s="5"/>
-      <c r="AA55" s="1"/>
-      <c r="AB55" s="1"/>
-      <c r="AC55" s="1"/>
-      <c r="AD55" s="5"/>
+      <c r="Z55" s="9"/>
+      <c r="AA55" s="26"/>
+      <c r="AB55" s="15"/>
+      <c r="AC55" s="17"/>
+      <c r="AD55" s="10"/>
       <c r="AE55" s="6"/>
-      <c r="AF55" s="5"/>
-      <c r="AG55" s="1"/>
+      <c r="AF55" s="9"/>
+      <c r="AG55" s="18"/>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
-      <c r="AJ55" s="1"/>
-      <c r="AK55" s="5"/>
+      <c r="AJ55" s="19"/>
+      <c r="AK55" s="10"/>
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
       <c r="AN55" s="6"/>
@@ -5729,7 +6025,7 @@
       <c r="CN55" s="2"/>
       <c r="CO55" s="2"/>
     </row>
-    <row r="56" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -5755,18 +6051,18 @@
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
-      <c r="Z56" s="5"/>
-      <c r="AA56" s="1"/>
-      <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
-      <c r="AD56" s="5"/>
+      <c r="Z56" s="9"/>
+      <c r="AA56" s="27"/>
+      <c r="AB56" s="20"/>
+      <c r="AC56" s="22"/>
+      <c r="AD56" s="10"/>
       <c r="AE56" s="6"/>
-      <c r="AF56" s="5"/>
-      <c r="AG56" s="1"/>
-      <c r="AH56" s="1"/>
-      <c r="AI56" s="1"/>
-      <c r="AJ56" s="1"/>
-      <c r="AK56" s="5"/>
+      <c r="AF56" s="9"/>
+      <c r="AG56" s="20"/>
+      <c r="AH56" s="21"/>
+      <c r="AI56" s="21"/>
+      <c r="AJ56" s="22"/>
+      <c r="AK56" s="10"/>
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
       <c r="AN56" s="6"/>
@@ -5824,7 +6120,7 @@
       <c r="CN56" s="2"/>
       <c r="CO56" s="2"/>
     </row>
-    <row r="57" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -5851,16 +6147,16 @@
       <c r="X57" s="5"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
-      <c r="AA57" s="5"/>
-      <c r="AB57" s="5"/>
-      <c r="AC57" s="5"/>
+      <c r="AA57" s="14"/>
+      <c r="AB57" s="14"/>
+      <c r="AC57" s="14"/>
       <c r="AD57" s="5"/>
       <c r="AE57" s="5"/>
       <c r="AF57" s="5"/>
-      <c r="AG57" s="5"/>
-      <c r="AH57" s="5"/>
-      <c r="AI57" s="5"/>
-      <c r="AJ57" s="5"/>
+      <c r="AG57" s="23"/>
+      <c r="AH57" s="23"/>
+      <c r="AI57" s="23"/>
+      <c r="AJ57" s="23"/>
       <c r="AK57" s="5"/>
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
@@ -5951,12 +6247,12 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="5"/>
       <c r="AE58" s="6"/>
-      <c r="AF58" s="5"/>
-      <c r="AG58" s="1"/>
-      <c r="AH58" s="1"/>
-      <c r="AI58" s="1"/>
-      <c r="AJ58" s="1"/>
-      <c r="AK58" s="5"/>
+      <c r="AF58" s="9"/>
+      <c r="AG58" s="15"/>
+      <c r="AH58" s="16"/>
+      <c r="AI58" s="16"/>
+      <c r="AJ58" s="17"/>
+      <c r="AK58" s="10"/>
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
       <c r="AN58" s="6"/>
@@ -6046,12 +6342,12 @@
       <c r="AC59" s="1"/>
       <c r="AD59" s="5"/>
       <c r="AE59" s="6"/>
-      <c r="AF59" s="5"/>
-      <c r="AG59" s="1"/>
+      <c r="AF59" s="9"/>
+      <c r="AG59" s="18"/>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
-      <c r="AJ59" s="1"/>
-      <c r="AK59" s="5"/>
+      <c r="AJ59" s="19"/>
+      <c r="AK59" s="10"/>
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
       <c r="AN59" s="6"/>
@@ -6109,7 +6405,7 @@
       <c r="CN59" s="2"/>
       <c r="CO59" s="2"/>
     </row>
-    <row r="60" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -6141,12 +6437,12 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="5"/>
       <c r="AE60" s="6"/>
-      <c r="AF60" s="5"/>
-      <c r="AG60" s="1"/>
-      <c r="AH60" s="1"/>
-      <c r="AI60" s="1"/>
-      <c r="AJ60" s="1"/>
-      <c r="AK60" s="5"/>
+      <c r="AF60" s="9"/>
+      <c r="AG60" s="20"/>
+      <c r="AH60" s="21"/>
+      <c r="AI60" s="21"/>
+      <c r="AJ60" s="22"/>
+      <c r="AK60" s="10"/>
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
       <c r="AN60" s="6"/>
@@ -6236,12 +6532,12 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="5"/>
       <c r="AE61" s="6"/>
-      <c r="AF61" s="5"/>
-      <c r="AG61" s="1"/>
-      <c r="AH61" s="1"/>
-      <c r="AI61" s="1"/>
-      <c r="AJ61" s="1"/>
-      <c r="AK61" s="5"/>
+      <c r="AF61" s="9"/>
+      <c r="AG61" s="15"/>
+      <c r="AH61" s="17"/>
+      <c r="AI61" s="15"/>
+      <c r="AJ61" s="17"/>
+      <c r="AK61" s="10"/>
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
       <c r="AN61" s="6"/>
@@ -6299,7 +6595,7 @@
       <c r="CN61" s="2"/>
       <c r="CO61" s="2"/>
     </row>
-    <row r="62" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -6331,12 +6627,12 @@
       <c r="AC62" s="1"/>
       <c r="AD62" s="5"/>
       <c r="AE62" s="6"/>
-      <c r="AF62" s="5"/>
-      <c r="AG62" s="1"/>
-      <c r="AH62" s="1"/>
-      <c r="AI62" s="1"/>
-      <c r="AJ62" s="1"/>
-      <c r="AK62" s="5"/>
+      <c r="AF62" s="9"/>
+      <c r="AG62" s="20"/>
+      <c r="AH62" s="22"/>
+      <c r="AI62" s="20"/>
+      <c r="AJ62" s="22"/>
+      <c r="AK62" s="10"/>
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
       <c r="AN62" s="6"/>
@@ -6394,7 +6690,7 @@
       <c r="CN62" s="2"/>
       <c r="CO62" s="2"/>
     </row>
-    <row r="63" spans="1:93" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:93" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -6427,10 +6723,10 @@
       <c r="AD63" s="5"/>
       <c r="AE63" s="5"/>
       <c r="AF63" s="5"/>
-      <c r="AG63" s="5"/>
-      <c r="AH63" s="5"/>
-      <c r="AI63" s="5"/>
-      <c r="AJ63" s="5"/>
+      <c r="AG63" s="23"/>
+      <c r="AH63" s="23"/>
+      <c r="AI63" s="23"/>
+      <c r="AJ63" s="23"/>
       <c r="AK63" s="5"/>
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
@@ -6521,12 +6817,12 @@
       <c r="AC64" s="1"/>
       <c r="AD64" s="5"/>
       <c r="AE64" s="6"/>
-      <c r="AF64" s="5"/>
-      <c r="AG64" s="1"/>
-      <c r="AH64" s="1"/>
-      <c r="AI64" s="1"/>
-      <c r="AJ64" s="1"/>
-      <c r="AK64" s="5"/>
+      <c r="AF64" s="9"/>
+      <c r="AG64" s="15"/>
+      <c r="AH64" s="17"/>
+      <c r="AI64" s="15"/>
+      <c r="AJ64" s="17"/>
+      <c r="AK64" s="10"/>
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
       <c r="AN64" s="6"/>
@@ -6616,12 +6912,12 @@
       <c r="AC65" s="1"/>
       <c r="AD65" s="5"/>
       <c r="AE65" s="6"/>
-      <c r="AF65" s="5"/>
-      <c r="AG65" s="1"/>
-      <c r="AH65" s="1"/>
-      <c r="AI65" s="1"/>
-      <c r="AJ65" s="1"/>
-      <c r="AK65" s="5"/>
+      <c r="AF65" s="9"/>
+      <c r="AG65" s="18"/>
+      <c r="AH65" s="19"/>
+      <c r="AI65" s="18"/>
+      <c r="AJ65" s="19"/>
+      <c r="AK65" s="10"/>
       <c r="AL65" s="5"/>
       <c r="AM65" s="5"/>
       <c r="AN65" s="6"/>
@@ -6679,7 +6975,7 @@
       <c r="CN65" s="2"/>
       <c r="CO65" s="2"/>
     </row>
-    <row r="66" spans="1:152" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:152" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -6711,12 +7007,12 @@
       <c r="AC66" s="1"/>
       <c r="AD66" s="5"/>
       <c r="AE66" s="6"/>
-      <c r="AF66" s="5"/>
-      <c r="AG66" s="1"/>
-      <c r="AH66" s="1"/>
-      <c r="AI66" s="1"/>
-      <c r="AJ66" s="1"/>
-      <c r="AK66" s="5"/>
+      <c r="AF66" s="9"/>
+      <c r="AG66" s="20"/>
+      <c r="AH66" s="22"/>
+      <c r="AI66" s="20"/>
+      <c r="AJ66" s="22"/>
+      <c r="AK66" s="10"/>
       <c r="AL66" s="5"/>
       <c r="AM66" s="5"/>
       <c r="AN66" s="6"/>
@@ -6774,7 +7070,7 @@
       <c r="CN66" s="2"/>
       <c r="CO66" s="2"/>
     </row>
-    <row r="67" spans="1:152" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:152" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -6807,10 +7103,10 @@
       <c r="AD67" s="5"/>
       <c r="AE67" s="5"/>
       <c r="AF67" s="5"/>
-      <c r="AG67" s="5"/>
-      <c r="AH67" s="5"/>
-      <c r="AI67" s="5"/>
-      <c r="AJ67" s="5"/>
+      <c r="AG67" s="23"/>
+      <c r="AH67" s="23"/>
+      <c r="AI67" s="23"/>
+      <c r="AJ67" s="23"/>
       <c r="AK67" s="5"/>
       <c r="AL67" s="5"/>
       <c r="AM67" s="5"/>
@@ -6901,12 +7197,12 @@
       <c r="AC68" s="1"/>
       <c r="AD68" s="5"/>
       <c r="AE68" s="6"/>
-      <c r="AF68" s="5"/>
-      <c r="AG68" s="1"/>
-      <c r="AH68" s="1"/>
-      <c r="AI68" s="1"/>
-      <c r="AJ68" s="1"/>
-      <c r="AK68" s="5"/>
+      <c r="AF68" s="9"/>
+      <c r="AG68" s="15"/>
+      <c r="AH68" s="17"/>
+      <c r="AI68" s="15"/>
+      <c r="AJ68" s="17"/>
+      <c r="AK68" s="10"/>
       <c r="AL68" s="5"/>
       <c r="AM68" s="5"/>
       <c r="AN68" s="6"/>
@@ -6996,12 +7292,12 @@
       <c r="AC69" s="1"/>
       <c r="AD69" s="5"/>
       <c r="AE69" s="6"/>
-      <c r="AF69" s="5"/>
-      <c r="AG69" s="1"/>
-      <c r="AH69" s="1"/>
-      <c r="AI69" s="1"/>
-      <c r="AJ69" s="1"/>
-      <c r="AK69" s="5"/>
+      <c r="AF69" s="9"/>
+      <c r="AG69" s="18"/>
+      <c r="AH69" s="19"/>
+      <c r="AI69" s="18"/>
+      <c r="AJ69" s="19"/>
+      <c r="AK69" s="10"/>
       <c r="AL69" s="5"/>
       <c r="AM69" s="5"/>
       <c r="AN69" s="6"/>
@@ -7091,12 +7387,12 @@
       <c r="AC70" s="1"/>
       <c r="AD70" s="5"/>
       <c r="AE70" s="6"/>
-      <c r="AF70" s="5"/>
-      <c r="AG70" s="1"/>
-      <c r="AH70" s="1"/>
-      <c r="AI70" s="1"/>
-      <c r="AJ70" s="1"/>
-      <c r="AK70" s="5"/>
+      <c r="AF70" s="9"/>
+      <c r="AG70" s="18"/>
+      <c r="AH70" s="19"/>
+      <c r="AI70" s="18"/>
+      <c r="AJ70" s="19"/>
+      <c r="AK70" s="10"/>
       <c r="AL70" s="5"/>
       <c r="AM70" s="5"/>
       <c r="AN70" s="6"/>
@@ -7154,7 +7450,7 @@
       <c r="CN70" s="2"/>
       <c r="CO70" s="2"/>
     </row>
-    <row r="71" spans="1:152" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:152" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -7186,12 +7482,12 @@
       <c r="AC71" s="1"/>
       <c r="AD71" s="5"/>
       <c r="AE71" s="6"/>
-      <c r="AF71" s="5"/>
-      <c r="AG71" s="1"/>
-      <c r="AH71" s="1"/>
-      <c r="AI71" s="1"/>
-      <c r="AJ71" s="1"/>
-      <c r="AK71" s="5"/>
+      <c r="AF71" s="9"/>
+      <c r="AG71" s="20"/>
+      <c r="AH71" s="22"/>
+      <c r="AI71" s="20"/>
+      <c r="AJ71" s="22"/>
+      <c r="AK71" s="10"/>
       <c r="AL71" s="5"/>
       <c r="AM71" s="5"/>
       <c r="AN71" s="6"/>
@@ -7249,7 +7545,7 @@
       <c r="CN71" s="2"/>
       <c r="CO71" s="2"/>
     </row>
-    <row r="72" spans="1:152" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:152" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -7282,10 +7578,10 @@
       <c r="AD72" s="5"/>
       <c r="AE72" s="5"/>
       <c r="AF72" s="5"/>
-      <c r="AG72" s="5"/>
-      <c r="AH72" s="5"/>
-      <c r="AI72" s="5"/>
-      <c r="AJ72" s="5"/>
+      <c r="AG72" s="23"/>
+      <c r="AH72" s="23"/>
+      <c r="AI72" s="23"/>
+      <c r="AJ72" s="23"/>
       <c r="AK72" s="5"/>
       <c r="AL72" s="5"/>
       <c r="AM72" s="5"/>
@@ -7376,12 +7672,12 @@
       <c r="AC73" s="1"/>
       <c r="AD73" s="5"/>
       <c r="AE73" s="6"/>
-      <c r="AF73" s="5"/>
-      <c r="AG73" s="1"/>
-      <c r="AH73" s="1"/>
-      <c r="AI73" s="1"/>
-      <c r="AJ73" s="1"/>
-      <c r="AK73" s="5"/>
+      <c r="AF73" s="9"/>
+      <c r="AG73" s="15"/>
+      <c r="AH73" s="16"/>
+      <c r="AI73" s="16"/>
+      <c r="AJ73" s="17"/>
+      <c r="AK73" s="10"/>
       <c r="AL73" s="5"/>
       <c r="AM73" s="5"/>
       <c r="AN73" s="6"/>
@@ -7471,12 +7767,12 @@
       <c r="AC74" s="1"/>
       <c r="AD74" s="5"/>
       <c r="AE74" s="6"/>
-      <c r="AF74" s="5"/>
-      <c r="AG74" s="1"/>
+      <c r="AF74" s="9"/>
+      <c r="AG74" s="18"/>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
-      <c r="AJ74" s="1"/>
-      <c r="AK74" s="5"/>
+      <c r="AJ74" s="19"/>
+      <c r="AK74" s="10"/>
       <c r="AL74" s="5"/>
       <c r="AM74" s="5"/>
       <c r="AN74" s="6"/>
@@ -7534,7 +7830,7 @@
       <c r="CN74" s="2"/>
       <c r="CO74" s="2"/>
     </row>
-    <row r="75" spans="1:152" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:152" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -7566,12 +7862,12 @@
       <c r="AC75" s="1"/>
       <c r="AD75" s="5"/>
       <c r="AE75" s="6"/>
-      <c r="AF75" s="5"/>
-      <c r="AG75" s="1"/>
-      <c r="AH75" s="1"/>
-      <c r="AI75" s="1"/>
-      <c r="AJ75" s="1"/>
-      <c r="AK75" s="5"/>
+      <c r="AF75" s="9"/>
+      <c r="AG75" s="20"/>
+      <c r="AH75" s="21"/>
+      <c r="AI75" s="21"/>
+      <c r="AJ75" s="22"/>
+      <c r="AK75" s="10"/>
       <c r="AL75" s="5"/>
       <c r="AM75" s="5"/>
       <c r="AN75" s="6"/>
@@ -7629,7 +7925,7 @@
       <c r="CN75" s="2"/>
       <c r="CO75" s="2"/>
     </row>
-    <row r="76" spans="1:152" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:152" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -7662,10 +7958,10 @@
       <c r="AD76" s="5"/>
       <c r="AE76" s="5"/>
       <c r="AF76" s="5"/>
-      <c r="AG76" s="5"/>
-      <c r="AH76" s="5"/>
-      <c r="AI76" s="5"/>
-      <c r="AJ76" s="5"/>
+      <c r="AG76" s="23"/>
+      <c r="AH76" s="23"/>
+      <c r="AI76" s="23"/>
+      <c r="AJ76" s="23"/>
       <c r="AK76" s="5"/>
       <c r="AL76" s="5"/>
       <c r="AM76" s="5"/>
@@ -7756,12 +8052,12 @@
       <c r="AC77" s="1"/>
       <c r="AD77" s="5"/>
       <c r="AE77" s="6"/>
-      <c r="AF77" s="5"/>
-      <c r="AG77" s="1"/>
-      <c r="AH77" s="1"/>
-      <c r="AI77" s="1"/>
-      <c r="AJ77" s="1"/>
-      <c r="AK77" s="5"/>
+      <c r="AF77" s="9"/>
+      <c r="AG77" s="15"/>
+      <c r="AH77" s="17"/>
+      <c r="AI77" s="15"/>
+      <c r="AJ77" s="17"/>
+      <c r="AK77" s="10"/>
       <c r="AL77" s="5"/>
       <c r="AM77" s="5"/>
       <c r="AN77" s="6"/>
@@ -7851,12 +8147,12 @@
       <c r="AC78" s="1"/>
       <c r="AD78" s="5"/>
       <c r="AE78" s="6"/>
-      <c r="AF78" s="5"/>
-      <c r="AG78" s="1"/>
-      <c r="AH78" s="1"/>
-      <c r="AI78" s="1"/>
-      <c r="AJ78" s="1"/>
-      <c r="AK78" s="5"/>
+      <c r="AF78" s="9"/>
+      <c r="AG78" s="18"/>
+      <c r="AH78" s="19"/>
+      <c r="AI78" s="18"/>
+      <c r="AJ78" s="19"/>
+      <c r="AK78" s="10"/>
       <c r="AL78" s="5"/>
       <c r="AM78" s="5"/>
       <c r="AN78" s="6"/>
@@ -7916,7 +8212,7 @@
       <c r="EU78" s="3"/>
       <c r="EV78" s="3"/>
     </row>
-    <row r="79" spans="1:152" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:152" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -7948,12 +8244,12 @@
       <c r="AC79" s="1"/>
       <c r="AD79" s="5"/>
       <c r="AE79" s="6"/>
-      <c r="AF79" s="5"/>
-      <c r="AG79" s="1"/>
-      <c r="AH79" s="1"/>
-      <c r="AI79" s="1"/>
-      <c r="AJ79" s="1"/>
-      <c r="AK79" s="5"/>
+      <c r="AF79" s="9"/>
+      <c r="AG79" s="20"/>
+      <c r="AH79" s="22"/>
+      <c r="AI79" s="20"/>
+      <c r="AJ79" s="22"/>
+      <c r="AK79" s="10"/>
       <c r="AL79" s="5"/>
       <c r="AM79" s="5"/>
       <c r="AN79" s="6"/>
@@ -8046,10 +8342,10 @@
       <c r="AD80" s="5"/>
       <c r="AE80" s="5"/>
       <c r="AF80" s="5"/>
-      <c r="AG80" s="5"/>
-      <c r="AH80" s="5"/>
-      <c r="AI80" s="5"/>
-      <c r="AJ80" s="5"/>
+      <c r="AG80" s="14"/>
+      <c r="AH80" s="14"/>
+      <c r="AI80" s="14"/>
+      <c r="AJ80" s="14"/>
       <c r="AK80" s="5"/>
       <c r="AL80" s="5"/>
       <c r="AM80" s="5"/>
